--- a/public/assets/templates/cliniq-patient-account-import.xlsx
+++ b/public/assets/templates/cliniq-patient-account-import.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Patient Accounts" sheetId="1" r:id="Rd9c28c8d59ff459e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R6a818c15a5a64578"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Patient Accounts" sheetId="1" r:id="R722db95c9aac474b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R6192eb39b0f7498f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52,7 +52,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -89,8 +89,18 @@
         <x:fgColor rgb="FFE8F6EC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF23422C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7D6"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="19">
+  <x:borders count="20">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -236,11 +246,16 @@
         <x:color rgb="FFE8D99A"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFDCE6DF"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="74">
+  <x:cellXfs count="85">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -377,6 +392,25 @@
     <x:xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -590,6 +624,7 @@
     <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="32" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -626,6 +661,9 @@
       <x:c r="K1" s="61" t="str">
         <x:v>Academic Year</x:v>
       </x:c>
+      <x:c r="L1" s="78" t="str">
+        <x:v>Access Status</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="17"/>
@@ -639,6 +677,7 @@
       <x:c r="I2" s="14"/>
       <x:c r="J2" s="14"/>
       <x:c r="K2" s="63"/>
+      <x:c r="L2" s="83"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="18"/>
@@ -652,6 +691,7 @@
       <x:c r="I3" s="15"/>
       <x:c r="J3" s="15"/>
       <x:c r="K3" s="64"/>
+      <x:c r="L3" s="83"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="18"/>
@@ -665,6 +705,7 @@
       <x:c r="I4" s="15"/>
       <x:c r="J4" s="15"/>
       <x:c r="K4" s="64"/>
+      <x:c r="L4" s="83"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="18"/>
@@ -678,6 +719,7 @@
       <x:c r="I5" s="15"/>
       <x:c r="J5" s="15"/>
       <x:c r="K5" s="64"/>
+      <x:c r="L5" s="83"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="18"/>
@@ -691,6 +733,7 @@
       <x:c r="I6" s="15"/>
       <x:c r="J6" s="15"/>
       <x:c r="K6" s="64"/>
+      <x:c r="L6" s="83"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="18"/>
@@ -704,6 +747,7 @@
       <x:c r="I7" s="15"/>
       <x:c r="J7" s="15"/>
       <x:c r="K7" s="64"/>
+      <x:c r="L7" s="83"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="18"/>
@@ -717,6 +761,7 @@
       <x:c r="I8" s="15"/>
       <x:c r="J8" s="15"/>
       <x:c r="K8" s="64"/>
+      <x:c r="L8" s="83"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="18"/>
@@ -730,6 +775,7 @@
       <x:c r="I9" s="15"/>
       <x:c r="J9" s="15"/>
       <x:c r="K9" s="64"/>
+      <x:c r="L9" s="83"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="18"/>
@@ -743,6 +789,7 @@
       <x:c r="I10" s="15"/>
       <x:c r="J10" s="15"/>
       <x:c r="K10" s="64"/>
+      <x:c r="L10" s="83"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="18"/>
@@ -756,6 +803,7 @@
       <x:c r="I11" s="15"/>
       <x:c r="J11" s="15"/>
       <x:c r="K11" s="64"/>
+      <x:c r="L11" s="83"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="18"/>
@@ -769,6 +817,7 @@
       <x:c r="I12" s="15"/>
       <x:c r="J12" s="15"/>
       <x:c r="K12" s="64"/>
+      <x:c r="L12" s="83"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="18"/>
@@ -782,6 +831,7 @@
       <x:c r="I13" s="15"/>
       <x:c r="J13" s="15"/>
       <x:c r="K13" s="64"/>
+      <x:c r="L13" s="83"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="18"/>
@@ -795,6 +845,7 @@
       <x:c r="I14" s="15"/>
       <x:c r="J14" s="15"/>
       <x:c r="K14" s="64"/>
+      <x:c r="L14" s="83"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="18"/>
@@ -808,6 +859,7 @@
       <x:c r="I15" s="15"/>
       <x:c r="J15" s="15"/>
       <x:c r="K15" s="64"/>
+      <x:c r="L15" s="83"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="18"/>
@@ -821,6 +873,7 @@
       <x:c r="I16" s="15"/>
       <x:c r="J16" s="15"/>
       <x:c r="K16" s="64"/>
+      <x:c r="L16" s="83"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="18"/>
@@ -834,6 +887,7 @@
       <x:c r="I17" s="15"/>
       <x:c r="J17" s="15"/>
       <x:c r="K17" s="64"/>
+      <x:c r="L17" s="83"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="18"/>
@@ -847,6 +901,7 @@
       <x:c r="I18" s="15"/>
       <x:c r="J18" s="15"/>
       <x:c r="K18" s="64"/>
+      <x:c r="L18" s="83"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="18"/>
@@ -860,6 +915,7 @@
       <x:c r="I19" s="15"/>
       <x:c r="J19" s="15"/>
       <x:c r="K19" s="64"/>
+      <x:c r="L19" s="83"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="18"/>
@@ -873,6 +929,7 @@
       <x:c r="I20" s="15"/>
       <x:c r="J20" s="15"/>
       <x:c r="K20" s="64"/>
+      <x:c r="L20" s="83"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="18"/>
@@ -886,6 +943,7 @@
       <x:c r="I21" s="15"/>
       <x:c r="J21" s="15"/>
       <x:c r="K21" s="64"/>
+      <x:c r="L21" s="83"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="18"/>
@@ -899,6 +957,7 @@
       <x:c r="I22" s="15"/>
       <x:c r="J22" s="15"/>
       <x:c r="K22" s="64"/>
+      <x:c r="L22" s="83"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="18"/>
@@ -912,6 +971,7 @@
       <x:c r="I23" s="15"/>
       <x:c r="J23" s="15"/>
       <x:c r="K23" s="64"/>
+      <x:c r="L23" s="83"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="18"/>
@@ -925,6 +985,7 @@
       <x:c r="I24" s="15"/>
       <x:c r="J24" s="15"/>
       <x:c r="K24" s="64"/>
+      <x:c r="L24" s="83"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="18"/>
@@ -938,6 +999,7 @@
       <x:c r="I25" s="15"/>
       <x:c r="J25" s="15"/>
       <x:c r="K25" s="64"/>
+      <x:c r="L25" s="83"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="18"/>
@@ -951,6 +1013,7 @@
       <x:c r="I26" s="15"/>
       <x:c r="J26" s="15"/>
       <x:c r="K26" s="64"/>
+      <x:c r="L26" s="83"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="18"/>
@@ -964,6 +1027,7 @@
       <x:c r="I27" s="15"/>
       <x:c r="J27" s="15"/>
       <x:c r="K27" s="64"/>
+      <x:c r="L27" s="83"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="18"/>
@@ -977,6 +1041,7 @@
       <x:c r="I28" s="15"/>
       <x:c r="J28" s="15"/>
       <x:c r="K28" s="64"/>
+      <x:c r="L28" s="83"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="18"/>
@@ -990,6 +1055,7 @@
       <x:c r="I29" s="15"/>
       <x:c r="J29" s="15"/>
       <x:c r="K29" s="64"/>
+      <x:c r="L29" s="83"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="18"/>
@@ -1003,6 +1069,7 @@
       <x:c r="I30" s="15"/>
       <x:c r="J30" s="15"/>
       <x:c r="K30" s="64"/>
+      <x:c r="L30" s="83"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="18"/>
@@ -1016,6 +1083,7 @@
       <x:c r="I31" s="15"/>
       <x:c r="J31" s="15"/>
       <x:c r="K31" s="64"/>
+      <x:c r="L31" s="83"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="18"/>
@@ -1029,6 +1097,7 @@
       <x:c r="I32" s="15"/>
       <x:c r="J32" s="15"/>
       <x:c r="K32" s="64"/>
+      <x:c r="L32" s="83"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="18"/>
@@ -1042,6 +1111,7 @@
       <x:c r="I33" s="15"/>
       <x:c r="J33" s="15"/>
       <x:c r="K33" s="64"/>
+      <x:c r="L33" s="83"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="18"/>
@@ -1055,6 +1125,7 @@
       <x:c r="I34" s="15"/>
       <x:c r="J34" s="15"/>
       <x:c r="K34" s="64"/>
+      <x:c r="L34" s="83"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="18"/>
@@ -1068,6 +1139,7 @@
       <x:c r="I35" s="15"/>
       <x:c r="J35" s="15"/>
       <x:c r="K35" s="64"/>
+      <x:c r="L35" s="83"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="18"/>
@@ -1081,6 +1153,7 @@
       <x:c r="I36" s="15"/>
       <x:c r="J36" s="15"/>
       <x:c r="K36" s="64"/>
+      <x:c r="L36" s="83"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="18"/>
@@ -1094,6 +1167,7 @@
       <x:c r="I37" s="15"/>
       <x:c r="J37" s="15"/>
       <x:c r="K37" s="64"/>
+      <x:c r="L37" s="83"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="18"/>
@@ -1107,6 +1181,7 @@
       <x:c r="I38" s="15"/>
       <x:c r="J38" s="15"/>
       <x:c r="K38" s="64"/>
+      <x:c r="L38" s="83"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="18"/>
@@ -1120,6 +1195,7 @@
       <x:c r="I39" s="15"/>
       <x:c r="J39" s="15"/>
       <x:c r="K39" s="64"/>
+      <x:c r="L39" s="83"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="18"/>
@@ -1133,6 +1209,7 @@
       <x:c r="I40" s="15"/>
       <x:c r="J40" s="15"/>
       <x:c r="K40" s="64"/>
+      <x:c r="L40" s="83"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="18"/>
@@ -1146,6 +1223,7 @@
       <x:c r="I41" s="15"/>
       <x:c r="J41" s="15"/>
       <x:c r="K41" s="64"/>
+      <x:c r="L41" s="83"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="18"/>
@@ -1159,6 +1237,7 @@
       <x:c r="I42" s="15"/>
       <x:c r="J42" s="15"/>
       <x:c r="K42" s="64"/>
+      <x:c r="L42" s="83"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="18"/>
@@ -1172,6 +1251,7 @@
       <x:c r="I43" s="15"/>
       <x:c r="J43" s="15"/>
       <x:c r="K43" s="64"/>
+      <x:c r="L43" s="83"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="18"/>
@@ -1185,6 +1265,7 @@
       <x:c r="I44" s="15"/>
       <x:c r="J44" s="15"/>
       <x:c r="K44" s="64"/>
+      <x:c r="L44" s="83"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="18"/>
@@ -1198,6 +1279,7 @@
       <x:c r="I45" s="15"/>
       <x:c r="J45" s="15"/>
       <x:c r="K45" s="64"/>
+      <x:c r="L45" s="83"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="18"/>
@@ -1211,6 +1293,7 @@
       <x:c r="I46" s="15"/>
       <x:c r="J46" s="15"/>
       <x:c r="K46" s="64"/>
+      <x:c r="L46" s="83"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="18"/>
@@ -1224,6 +1307,7 @@
       <x:c r="I47" s="15"/>
       <x:c r="J47" s="15"/>
       <x:c r="K47" s="64"/>
+      <x:c r="L47" s="83"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="18"/>
@@ -1237,6 +1321,7 @@
       <x:c r="I48" s="15"/>
       <x:c r="J48" s="15"/>
       <x:c r="K48" s="64"/>
+      <x:c r="L48" s="83"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="18"/>
@@ -1250,6 +1335,7 @@
       <x:c r="I49" s="15"/>
       <x:c r="J49" s="15"/>
       <x:c r="K49" s="64"/>
+      <x:c r="L49" s="83"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="18"/>
@@ -1263,6 +1349,7 @@
       <x:c r="I50" s="15"/>
       <x:c r="J50" s="15"/>
       <x:c r="K50" s="64"/>
+      <x:c r="L50" s="83"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="18"/>
@@ -1276,6 +1363,7 @@
       <x:c r="I51" s="15"/>
       <x:c r="J51" s="15"/>
       <x:c r="K51" s="64"/>
+      <x:c r="L51" s="83"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="18"/>
@@ -1289,6 +1377,7 @@
       <x:c r="I52" s="15"/>
       <x:c r="J52" s="15"/>
       <x:c r="K52" s="64"/>
+      <x:c r="L52" s="83"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="18"/>
@@ -1302,6 +1391,7 @@
       <x:c r="I53" s="15"/>
       <x:c r="J53" s="15"/>
       <x:c r="K53" s="64"/>
+      <x:c r="L53" s="83"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="18"/>
@@ -1315,6 +1405,7 @@
       <x:c r="I54" s="15"/>
       <x:c r="J54" s="15"/>
       <x:c r="K54" s="64"/>
+      <x:c r="L54" s="83"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="18"/>
@@ -1328,6 +1419,7 @@
       <x:c r="I55" s="15"/>
       <x:c r="J55" s="15"/>
       <x:c r="K55" s="64"/>
+      <x:c r="L55" s="83"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="18"/>
@@ -1341,6 +1433,7 @@
       <x:c r="I56" s="15"/>
       <x:c r="J56" s="15"/>
       <x:c r="K56" s="64"/>
+      <x:c r="L56" s="83"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="18"/>
@@ -1354,6 +1447,7 @@
       <x:c r="I57" s="15"/>
       <x:c r="J57" s="15"/>
       <x:c r="K57" s="64"/>
+      <x:c r="L57" s="83"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="18"/>
@@ -1367,6 +1461,7 @@
       <x:c r="I58" s="15"/>
       <x:c r="J58" s="15"/>
       <x:c r="K58" s="64"/>
+      <x:c r="L58" s="83"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="18"/>
@@ -1380,6 +1475,7 @@
       <x:c r="I59" s="15"/>
       <x:c r="J59" s="15"/>
       <x:c r="K59" s="64"/>
+      <x:c r="L59" s="83"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="18"/>
@@ -1393,6 +1489,7 @@
       <x:c r="I60" s="15"/>
       <x:c r="J60" s="15"/>
       <x:c r="K60" s="64"/>
+      <x:c r="L60" s="83"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="18"/>
@@ -1406,6 +1503,7 @@
       <x:c r="I61" s="15"/>
       <x:c r="J61" s="15"/>
       <x:c r="K61" s="64"/>
+      <x:c r="L61" s="83"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="18"/>
@@ -1419,6 +1517,7 @@
       <x:c r="I62" s="15"/>
       <x:c r="J62" s="15"/>
       <x:c r="K62" s="64"/>
+      <x:c r="L62" s="83"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="18"/>
@@ -1432,6 +1531,7 @@
       <x:c r="I63" s="15"/>
       <x:c r="J63" s="15"/>
       <x:c r="K63" s="64"/>
+      <x:c r="L63" s="83"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="18"/>
@@ -1445,6 +1545,7 @@
       <x:c r="I64" s="15"/>
       <x:c r="J64" s="15"/>
       <x:c r="K64" s="64"/>
+      <x:c r="L64" s="83"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="18"/>
@@ -1458,6 +1559,7 @@
       <x:c r="I65" s="15"/>
       <x:c r="J65" s="15"/>
       <x:c r="K65" s="64"/>
+      <x:c r="L65" s="83"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="18"/>
@@ -1471,6 +1573,7 @@
       <x:c r="I66" s="15"/>
       <x:c r="J66" s="15"/>
       <x:c r="K66" s="64"/>
+      <x:c r="L66" s="83"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="18"/>
@@ -1484,6 +1587,7 @@
       <x:c r="I67" s="15"/>
       <x:c r="J67" s="15"/>
       <x:c r="K67" s="64"/>
+      <x:c r="L67" s="83"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="18"/>
@@ -1497,6 +1601,7 @@
       <x:c r="I68" s="15"/>
       <x:c r="J68" s="15"/>
       <x:c r="K68" s="64"/>
+      <x:c r="L68" s="83"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="18"/>
@@ -1510,6 +1615,7 @@
       <x:c r="I69" s="15"/>
       <x:c r="J69" s="15"/>
       <x:c r="K69" s="64"/>
+      <x:c r="L69" s="83"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="18"/>
@@ -1523,6 +1629,7 @@
       <x:c r="I70" s="15"/>
       <x:c r="J70" s="15"/>
       <x:c r="K70" s="64"/>
+      <x:c r="L70" s="83"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="18"/>
@@ -1536,6 +1643,7 @@
       <x:c r="I71" s="15"/>
       <x:c r="J71" s="15"/>
       <x:c r="K71" s="64"/>
+      <x:c r="L71" s="83"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="18"/>
@@ -1549,6 +1657,7 @@
       <x:c r="I72" s="15"/>
       <x:c r="J72" s="15"/>
       <x:c r="K72" s="64"/>
+      <x:c r="L72" s="83"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="18"/>
@@ -1562,6 +1671,7 @@
       <x:c r="I73" s="15"/>
       <x:c r="J73" s="15"/>
       <x:c r="K73" s="64"/>
+      <x:c r="L73" s="83"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="18"/>
@@ -1575,6 +1685,7 @@
       <x:c r="I74" s="15"/>
       <x:c r="J74" s="15"/>
       <x:c r="K74" s="64"/>
+      <x:c r="L74" s="83"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="18"/>
@@ -1588,6 +1699,7 @@
       <x:c r="I75" s="15"/>
       <x:c r="J75" s="15"/>
       <x:c r="K75" s="64"/>
+      <x:c r="L75" s="83"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="18"/>
@@ -1601,6 +1713,7 @@
       <x:c r="I76" s="15"/>
       <x:c r="J76" s="15"/>
       <x:c r="K76" s="64"/>
+      <x:c r="L76" s="83"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="18"/>
@@ -1614,6 +1727,7 @@
       <x:c r="I77" s="15"/>
       <x:c r="J77" s="15"/>
       <x:c r="K77" s="64"/>
+      <x:c r="L77" s="83"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="18"/>
@@ -1627,6 +1741,7 @@
       <x:c r="I78" s="15"/>
       <x:c r="J78" s="15"/>
       <x:c r="K78" s="64"/>
+      <x:c r="L78" s="83"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="18"/>
@@ -1640,6 +1755,7 @@
       <x:c r="I79" s="15"/>
       <x:c r="J79" s="15"/>
       <x:c r="K79" s="64"/>
+      <x:c r="L79" s="83"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="18"/>
@@ -1653,6 +1769,7 @@
       <x:c r="I80" s="15"/>
       <x:c r="J80" s="15"/>
       <x:c r="K80" s="64"/>
+      <x:c r="L80" s="83"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="18"/>
@@ -1666,6 +1783,7 @@
       <x:c r="I81" s="15"/>
       <x:c r="J81" s="15"/>
       <x:c r="K81" s="64"/>
+      <x:c r="L81" s="83"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="18"/>
@@ -1679,6 +1797,7 @@
       <x:c r="I82" s="15"/>
       <x:c r="J82" s="15"/>
       <x:c r="K82" s="64"/>
+      <x:c r="L82" s="83"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="18"/>
@@ -1692,6 +1811,7 @@
       <x:c r="I83" s="15"/>
       <x:c r="J83" s="15"/>
       <x:c r="K83" s="64"/>
+      <x:c r="L83" s="83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="18"/>
@@ -1705,6 +1825,7 @@
       <x:c r="I84" s="15"/>
       <x:c r="J84" s="15"/>
       <x:c r="K84" s="64"/>
+      <x:c r="L84" s="83"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="18"/>
@@ -1718,6 +1839,7 @@
       <x:c r="I85" s="15"/>
       <x:c r="J85" s="15"/>
       <x:c r="K85" s="64"/>
+      <x:c r="L85" s="83"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="18"/>
@@ -1731,6 +1853,7 @@
       <x:c r="I86" s="15"/>
       <x:c r="J86" s="15"/>
       <x:c r="K86" s="64"/>
+      <x:c r="L86" s="83"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="18"/>
@@ -1744,6 +1867,7 @@
       <x:c r="I87" s="15"/>
       <x:c r="J87" s="15"/>
       <x:c r="K87" s="64"/>
+      <x:c r="L87" s="83"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="18"/>
@@ -1757,6 +1881,7 @@
       <x:c r="I88" s="15"/>
       <x:c r="J88" s="15"/>
       <x:c r="K88" s="64"/>
+      <x:c r="L88" s="83"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="18"/>
@@ -1770,6 +1895,7 @@
       <x:c r="I89" s="15"/>
       <x:c r="J89" s="15"/>
       <x:c r="K89" s="64"/>
+      <x:c r="L89" s="83"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="18"/>
@@ -1783,6 +1909,7 @@
       <x:c r="I90" s="15"/>
       <x:c r="J90" s="15"/>
       <x:c r="K90" s="64"/>
+      <x:c r="L90" s="83"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="18"/>
@@ -1796,6 +1923,7 @@
       <x:c r="I91" s="15"/>
       <x:c r="J91" s="15"/>
       <x:c r="K91" s="64"/>
+      <x:c r="L91" s="83"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="18"/>
@@ -1809,6 +1937,7 @@
       <x:c r="I92" s="15"/>
       <x:c r="J92" s="15"/>
       <x:c r="K92" s="64"/>
+      <x:c r="L92" s="83"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="18"/>
@@ -1822,6 +1951,7 @@
       <x:c r="I93" s="15"/>
       <x:c r="J93" s="15"/>
       <x:c r="K93" s="64"/>
+      <x:c r="L93" s="83"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="18"/>
@@ -1835,6 +1965,7 @@
       <x:c r="I94" s="15"/>
       <x:c r="J94" s="15"/>
       <x:c r="K94" s="64"/>
+      <x:c r="L94" s="83"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="18"/>
@@ -1848,6 +1979,7 @@
       <x:c r="I95" s="15"/>
       <x:c r="J95" s="15"/>
       <x:c r="K95" s="64"/>
+      <x:c r="L95" s="83"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="18"/>
@@ -1861,6 +1993,7 @@
       <x:c r="I96" s="15"/>
       <x:c r="J96" s="15"/>
       <x:c r="K96" s="64"/>
+      <x:c r="L96" s="83"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="18"/>
@@ -1874,6 +2007,7 @@
       <x:c r="I97" s="15"/>
       <x:c r="J97" s="15"/>
       <x:c r="K97" s="64"/>
+      <x:c r="L97" s="83"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="18"/>
@@ -1887,6 +2021,7 @@
       <x:c r="I98" s="15"/>
       <x:c r="J98" s="15"/>
       <x:c r="K98" s="64"/>
+      <x:c r="L98" s="83"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="18"/>
@@ -1900,6 +2035,7 @@
       <x:c r="I99" s="15"/>
       <x:c r="J99" s="15"/>
       <x:c r="K99" s="64"/>
+      <x:c r="L99" s="83"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="18"/>
@@ -1913,6 +2049,7 @@
       <x:c r="I100" s="15"/>
       <x:c r="J100" s="15"/>
       <x:c r="K100" s="64"/>
+      <x:c r="L100" s="83"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="19"/>
@@ -1926,6 +2063,7 @@
       <x:c r="I101" s="16"/>
       <x:c r="J101" s="16"/>
       <x:c r="K101" s="64"/>
+      <x:c r="L101" s="83"/>
     </x:row>
     <x:row r="102">
       <x:c r="G102" s="57"/>
@@ -1933,6 +2071,7 @@
       <x:c r="I102"/>
       <x:c r="J102"/>
       <x:c r="K102" s="64"/>
+      <x:c r="L102" s="83"/>
     </x:row>
     <x:row r="103">
       <x:c r="G103" s="57"/>
@@ -1940,6 +2079,7 @@
       <x:c r="I103"/>
       <x:c r="J103"/>
       <x:c r="K103" s="64"/>
+      <x:c r="L103" s="83"/>
     </x:row>
     <x:row r="104">
       <x:c r="G104" s="57"/>
@@ -1947,6 +2087,7 @@
       <x:c r="I104"/>
       <x:c r="J104"/>
       <x:c r="K104" s="64"/>
+      <x:c r="L104" s="83"/>
     </x:row>
     <x:row r="105">
       <x:c r="G105" s="57"/>
@@ -1954,6 +2095,7 @@
       <x:c r="I105"/>
       <x:c r="J105"/>
       <x:c r="K105" s="64"/>
+      <x:c r="L105" s="83"/>
     </x:row>
     <x:row r="106">
       <x:c r="G106" s="57"/>
@@ -1961,6 +2103,7 @@
       <x:c r="I106"/>
       <x:c r="J106"/>
       <x:c r="K106" s="64"/>
+      <x:c r="L106" s="83"/>
     </x:row>
     <x:row r="107">
       <x:c r="G107" s="57"/>
@@ -1968,6 +2111,7 @@
       <x:c r="I107"/>
       <x:c r="J107"/>
       <x:c r="K107" s="64"/>
+      <x:c r="L107" s="83"/>
     </x:row>
     <x:row r="108">
       <x:c r="G108" s="57"/>
@@ -1975,6 +2119,7 @@
       <x:c r="I108"/>
       <x:c r="J108"/>
       <x:c r="K108" s="64"/>
+      <x:c r="L108" s="83"/>
     </x:row>
     <x:row r="109">
       <x:c r="G109" s="57"/>
@@ -1982,6 +2127,7 @@
       <x:c r="I109"/>
       <x:c r="J109"/>
       <x:c r="K109" s="64"/>
+      <x:c r="L109" s="83"/>
     </x:row>
     <x:row r="110">
       <x:c r="G110" s="57"/>
@@ -1989,6 +2135,7 @@
       <x:c r="I110"/>
       <x:c r="J110"/>
       <x:c r="K110" s="64"/>
+      <x:c r="L110" s="83"/>
     </x:row>
     <x:row r="111">
       <x:c r="G111" s="57"/>
@@ -1996,6 +2143,7 @@
       <x:c r="I111"/>
       <x:c r="J111"/>
       <x:c r="K111" s="64"/>
+      <x:c r="L111" s="83"/>
     </x:row>
     <x:row r="112">
       <x:c r="G112" s="57"/>
@@ -2003,6 +2151,7 @@
       <x:c r="I112"/>
       <x:c r="J112"/>
       <x:c r="K112" s="64"/>
+      <x:c r="L112" s="83"/>
     </x:row>
     <x:row r="113">
       <x:c r="G113" s="57"/>
@@ -2010,6 +2159,7 @@
       <x:c r="I113"/>
       <x:c r="J113"/>
       <x:c r="K113" s="64"/>
+      <x:c r="L113" s="83"/>
     </x:row>
     <x:row r="114">
       <x:c r="G114" s="57"/>
@@ -2017,6 +2167,7 @@
       <x:c r="I114"/>
       <x:c r="J114"/>
       <x:c r="K114" s="64"/>
+      <x:c r="L114" s="83"/>
     </x:row>
     <x:row r="115">
       <x:c r="G115" s="57"/>
@@ -2024,6 +2175,7 @@
       <x:c r="I115"/>
       <x:c r="J115"/>
       <x:c r="K115" s="64"/>
+      <x:c r="L115" s="83"/>
     </x:row>
     <x:row r="116">
       <x:c r="G116" s="57"/>
@@ -2031,6 +2183,7 @@
       <x:c r="I116"/>
       <x:c r="J116"/>
       <x:c r="K116" s="64"/>
+      <x:c r="L116" s="83"/>
     </x:row>
     <x:row r="117">
       <x:c r="G117" s="57"/>
@@ -2038,6 +2191,7 @@
       <x:c r="I117"/>
       <x:c r="J117"/>
       <x:c r="K117" s="64"/>
+      <x:c r="L117" s="83"/>
     </x:row>
     <x:row r="118">
       <x:c r="G118" s="57"/>
@@ -2045,6 +2199,7 @@
       <x:c r="I118"/>
       <x:c r="J118"/>
       <x:c r="K118" s="64"/>
+      <x:c r="L118" s="83"/>
     </x:row>
     <x:row r="119">
       <x:c r="G119" s="57"/>
@@ -2052,6 +2207,7 @@
       <x:c r="I119"/>
       <x:c r="J119"/>
       <x:c r="K119" s="64"/>
+      <x:c r="L119" s="83"/>
     </x:row>
     <x:row r="120">
       <x:c r="G120" s="57"/>
@@ -2059,6 +2215,7 @@
       <x:c r="I120"/>
       <x:c r="J120"/>
       <x:c r="K120" s="64"/>
+      <x:c r="L120" s="83"/>
     </x:row>
     <x:row r="121">
       <x:c r="G121" s="57"/>
@@ -2066,6 +2223,7 @@
       <x:c r="I121"/>
       <x:c r="J121"/>
       <x:c r="K121" s="64"/>
+      <x:c r="L121" s="83"/>
     </x:row>
     <x:row r="122">
       <x:c r="G122" s="57"/>
@@ -2073,6 +2231,7 @@
       <x:c r="I122"/>
       <x:c r="J122"/>
       <x:c r="K122" s="64"/>
+      <x:c r="L122" s="83"/>
     </x:row>
     <x:row r="123">
       <x:c r="G123" s="57"/>
@@ -2080,6 +2239,7 @@
       <x:c r="I123"/>
       <x:c r="J123"/>
       <x:c r="K123" s="64"/>
+      <x:c r="L123" s="83"/>
     </x:row>
     <x:row r="124">
       <x:c r="G124" s="57"/>
@@ -2087,6 +2247,7 @@
       <x:c r="I124"/>
       <x:c r="J124"/>
       <x:c r="K124" s="64"/>
+      <x:c r="L124" s="83"/>
     </x:row>
     <x:row r="125">
       <x:c r="G125" s="57"/>
@@ -2094,6 +2255,7 @@
       <x:c r="I125"/>
       <x:c r="J125"/>
       <x:c r="K125" s="64"/>
+      <x:c r="L125" s="83"/>
     </x:row>
     <x:row r="126">
       <x:c r="G126" s="57"/>
@@ -2101,6 +2263,7 @@
       <x:c r="I126"/>
       <x:c r="J126"/>
       <x:c r="K126" s="64"/>
+      <x:c r="L126" s="83"/>
     </x:row>
     <x:row r="127">
       <x:c r="G127" s="57"/>
@@ -2108,6 +2271,7 @@
       <x:c r="I127"/>
       <x:c r="J127"/>
       <x:c r="K127" s="64"/>
+      <x:c r="L127" s="83"/>
     </x:row>
     <x:row r="128">
       <x:c r="G128" s="57"/>
@@ -2115,6 +2279,7 @@
       <x:c r="I128"/>
       <x:c r="J128"/>
       <x:c r="K128" s="64"/>
+      <x:c r="L128" s="83"/>
     </x:row>
     <x:row r="129">
       <x:c r="G129" s="57"/>
@@ -2122,6 +2287,7 @@
       <x:c r="I129"/>
       <x:c r="J129"/>
       <x:c r="K129" s="64"/>
+      <x:c r="L129" s="83"/>
     </x:row>
     <x:row r="130">
       <x:c r="G130" s="57"/>
@@ -2129,6 +2295,7 @@
       <x:c r="I130"/>
       <x:c r="J130"/>
       <x:c r="K130" s="64"/>
+      <x:c r="L130" s="83"/>
     </x:row>
     <x:row r="131">
       <x:c r="G131" s="57"/>
@@ -2136,6 +2303,7 @@
       <x:c r="I131"/>
       <x:c r="J131"/>
       <x:c r="K131" s="64"/>
+      <x:c r="L131" s="83"/>
     </x:row>
     <x:row r="132">
       <x:c r="G132" s="57"/>
@@ -2143,6 +2311,7 @@
       <x:c r="I132"/>
       <x:c r="J132"/>
       <x:c r="K132" s="64"/>
+      <x:c r="L132" s="83"/>
     </x:row>
     <x:row r="133">
       <x:c r="G133" s="57"/>
@@ -2150,6 +2319,7 @@
       <x:c r="I133"/>
       <x:c r="J133"/>
       <x:c r="K133" s="64"/>
+      <x:c r="L133" s="83"/>
     </x:row>
     <x:row r="134">
       <x:c r="G134" s="57"/>
@@ -2157,6 +2327,7 @@
       <x:c r="I134"/>
       <x:c r="J134"/>
       <x:c r="K134" s="64"/>
+      <x:c r="L134" s="83"/>
     </x:row>
     <x:row r="135">
       <x:c r="G135" s="57"/>
@@ -2164,6 +2335,7 @@
       <x:c r="I135"/>
       <x:c r="J135"/>
       <x:c r="K135" s="64"/>
+      <x:c r="L135" s="83"/>
     </x:row>
     <x:row r="136">
       <x:c r="G136" s="57"/>
@@ -2171,6 +2343,7 @@
       <x:c r="I136"/>
       <x:c r="J136"/>
       <x:c r="K136" s="64"/>
+      <x:c r="L136" s="83"/>
     </x:row>
     <x:row r="137">
       <x:c r="G137" s="57"/>
@@ -2178,6 +2351,7 @@
       <x:c r="I137"/>
       <x:c r="J137"/>
       <x:c r="K137" s="64"/>
+      <x:c r="L137" s="83"/>
     </x:row>
     <x:row r="138">
       <x:c r="G138" s="57"/>
@@ -2185,6 +2359,7 @@
       <x:c r="I138"/>
       <x:c r="J138"/>
       <x:c r="K138" s="64"/>
+      <x:c r="L138" s="83"/>
     </x:row>
     <x:row r="139">
       <x:c r="G139" s="57"/>
@@ -2192,6 +2367,7 @@
       <x:c r="I139"/>
       <x:c r="J139"/>
       <x:c r="K139" s="64"/>
+      <x:c r="L139" s="83"/>
     </x:row>
     <x:row r="140">
       <x:c r="G140" s="57"/>
@@ -2199,6 +2375,7 @@
       <x:c r="I140"/>
       <x:c r="J140"/>
       <x:c r="K140" s="64"/>
+      <x:c r="L140" s="83"/>
     </x:row>
     <x:row r="141">
       <x:c r="G141" s="57"/>
@@ -2206,6 +2383,7 @@
       <x:c r="I141"/>
       <x:c r="J141"/>
       <x:c r="K141" s="64"/>
+      <x:c r="L141" s="83"/>
     </x:row>
     <x:row r="142">
       <x:c r="G142" s="57"/>
@@ -2213,6 +2391,7 @@
       <x:c r="I142"/>
       <x:c r="J142"/>
       <x:c r="K142" s="64"/>
+      <x:c r="L142" s="83"/>
     </x:row>
     <x:row r="143">
       <x:c r="G143" s="57"/>
@@ -2220,6 +2399,7 @@
       <x:c r="I143"/>
       <x:c r="J143"/>
       <x:c r="K143" s="64"/>
+      <x:c r="L143" s="83"/>
     </x:row>
     <x:row r="144">
       <x:c r="G144" s="57"/>
@@ -2227,6 +2407,7 @@
       <x:c r="I144"/>
       <x:c r="J144"/>
       <x:c r="K144" s="64"/>
+      <x:c r="L144" s="83"/>
     </x:row>
     <x:row r="145">
       <x:c r="G145" s="57"/>
@@ -2234,6 +2415,7 @@
       <x:c r="I145"/>
       <x:c r="J145"/>
       <x:c r="K145" s="64"/>
+      <x:c r="L145" s="83"/>
     </x:row>
     <x:row r="146">
       <x:c r="G146" s="57"/>
@@ -2241,6 +2423,7 @@
       <x:c r="I146"/>
       <x:c r="J146"/>
       <x:c r="K146" s="64"/>
+      <x:c r="L146" s="83"/>
     </x:row>
     <x:row r="147">
       <x:c r="G147" s="57"/>
@@ -2248,6 +2431,7 @@
       <x:c r="I147"/>
       <x:c r="J147"/>
       <x:c r="K147" s="64"/>
+      <x:c r="L147" s="83"/>
     </x:row>
     <x:row r="148">
       <x:c r="G148" s="57"/>
@@ -2255,6 +2439,7 @@
       <x:c r="I148"/>
       <x:c r="J148"/>
       <x:c r="K148" s="64"/>
+      <x:c r="L148" s="83"/>
     </x:row>
     <x:row r="149">
       <x:c r="G149" s="57"/>
@@ -2262,6 +2447,7 @@
       <x:c r="I149"/>
       <x:c r="J149"/>
       <x:c r="K149" s="64"/>
+      <x:c r="L149" s="83"/>
     </x:row>
     <x:row r="150">
       <x:c r="G150" s="57"/>
@@ -2269,6 +2455,7 @@
       <x:c r="I150"/>
       <x:c r="J150"/>
       <x:c r="K150" s="64"/>
+      <x:c r="L150" s="83"/>
     </x:row>
     <x:row r="151">
       <x:c r="G151" s="57"/>
@@ -2276,6 +2463,7 @@
       <x:c r="I151"/>
       <x:c r="J151"/>
       <x:c r="K151" s="64"/>
+      <x:c r="L151" s="83"/>
     </x:row>
     <x:row r="152">
       <x:c r="G152" s="57"/>
@@ -2283,6 +2471,7 @@
       <x:c r="I152"/>
       <x:c r="J152"/>
       <x:c r="K152" s="64"/>
+      <x:c r="L152" s="83"/>
     </x:row>
     <x:row r="153">
       <x:c r="G153" s="57"/>
@@ -2290,6 +2479,7 @@
       <x:c r="I153"/>
       <x:c r="J153"/>
       <x:c r="K153" s="64"/>
+      <x:c r="L153" s="83"/>
     </x:row>
     <x:row r="154">
       <x:c r="G154" s="57"/>
@@ -2297,6 +2487,7 @@
       <x:c r="I154"/>
       <x:c r="J154"/>
       <x:c r="K154" s="64"/>
+      <x:c r="L154" s="83"/>
     </x:row>
     <x:row r="155">
       <x:c r="G155" s="57"/>
@@ -2304,6 +2495,7 @@
       <x:c r="I155"/>
       <x:c r="J155"/>
       <x:c r="K155" s="64"/>
+      <x:c r="L155" s="83"/>
     </x:row>
     <x:row r="156">
       <x:c r="G156" s="57"/>
@@ -2311,6 +2503,7 @@
       <x:c r="I156"/>
       <x:c r="J156"/>
       <x:c r="K156" s="64"/>
+      <x:c r="L156" s="83"/>
     </x:row>
     <x:row r="157">
       <x:c r="G157" s="57"/>
@@ -2318,6 +2511,7 @@
       <x:c r="I157"/>
       <x:c r="J157"/>
       <x:c r="K157" s="64"/>
+      <x:c r="L157" s="83"/>
     </x:row>
     <x:row r="158">
       <x:c r="G158" s="57"/>
@@ -2325,6 +2519,7 @@
       <x:c r="I158"/>
       <x:c r="J158"/>
       <x:c r="K158" s="64"/>
+      <x:c r="L158" s="83"/>
     </x:row>
     <x:row r="159">
       <x:c r="G159" s="57"/>
@@ -2332,6 +2527,7 @@
       <x:c r="I159"/>
       <x:c r="J159"/>
       <x:c r="K159" s="64"/>
+      <x:c r="L159" s="83"/>
     </x:row>
     <x:row r="160">
       <x:c r="G160" s="57"/>
@@ -2339,6 +2535,7 @@
       <x:c r="I160"/>
       <x:c r="J160"/>
       <x:c r="K160" s="64"/>
+      <x:c r="L160" s="83"/>
     </x:row>
     <x:row r="161">
       <x:c r="G161" s="57"/>
@@ -2346,6 +2543,7 @@
       <x:c r="I161"/>
       <x:c r="J161"/>
       <x:c r="K161" s="64"/>
+      <x:c r="L161" s="83"/>
     </x:row>
     <x:row r="162">
       <x:c r="G162" s="57"/>
@@ -2353,6 +2551,7 @@
       <x:c r="I162"/>
       <x:c r="J162"/>
       <x:c r="K162" s="64"/>
+      <x:c r="L162" s="83"/>
     </x:row>
     <x:row r="163">
       <x:c r="G163" s="57"/>
@@ -2360,6 +2559,7 @@
       <x:c r="I163"/>
       <x:c r="J163"/>
       <x:c r="K163" s="64"/>
+      <x:c r="L163" s="83"/>
     </x:row>
     <x:row r="164">
       <x:c r="G164" s="57"/>
@@ -2367,6 +2567,7 @@
       <x:c r="I164"/>
       <x:c r="J164"/>
       <x:c r="K164" s="64"/>
+      <x:c r="L164" s="83"/>
     </x:row>
     <x:row r="165">
       <x:c r="G165" s="57"/>
@@ -2374,6 +2575,7 @@
       <x:c r="I165"/>
       <x:c r="J165"/>
       <x:c r="K165" s="64"/>
+      <x:c r="L165" s="83"/>
     </x:row>
     <x:row r="166">
       <x:c r="G166" s="57"/>
@@ -2381,6 +2583,7 @@
       <x:c r="I166"/>
       <x:c r="J166"/>
       <x:c r="K166" s="64"/>
+      <x:c r="L166" s="83"/>
     </x:row>
     <x:row r="167">
       <x:c r="G167" s="57"/>
@@ -2388,6 +2591,7 @@
       <x:c r="I167"/>
       <x:c r="J167"/>
       <x:c r="K167" s="64"/>
+      <x:c r="L167" s="83"/>
     </x:row>
     <x:row r="168">
       <x:c r="G168" s="57"/>
@@ -2395,6 +2599,7 @@
       <x:c r="I168"/>
       <x:c r="J168"/>
       <x:c r="K168" s="64"/>
+      <x:c r="L168" s="83"/>
     </x:row>
     <x:row r="169">
       <x:c r="G169" s="57"/>
@@ -2402,6 +2607,7 @@
       <x:c r="I169"/>
       <x:c r="J169"/>
       <x:c r="K169" s="64"/>
+      <x:c r="L169" s="83"/>
     </x:row>
     <x:row r="170">
       <x:c r="G170" s="57"/>
@@ -2409,6 +2615,7 @@
       <x:c r="I170"/>
       <x:c r="J170"/>
       <x:c r="K170" s="64"/>
+      <x:c r="L170" s="83"/>
     </x:row>
     <x:row r="171">
       <x:c r="G171" s="57"/>
@@ -2416,6 +2623,7 @@
       <x:c r="I171"/>
       <x:c r="J171"/>
       <x:c r="K171" s="64"/>
+      <x:c r="L171" s="83"/>
     </x:row>
     <x:row r="172">
       <x:c r="G172" s="57"/>
@@ -2423,6 +2631,7 @@
       <x:c r="I172"/>
       <x:c r="J172"/>
       <x:c r="K172" s="64"/>
+      <x:c r="L172" s="83"/>
     </x:row>
     <x:row r="173">
       <x:c r="G173" s="57"/>
@@ -2430,6 +2639,7 @@
       <x:c r="I173"/>
       <x:c r="J173"/>
       <x:c r="K173" s="64"/>
+      <x:c r="L173" s="83"/>
     </x:row>
     <x:row r="174">
       <x:c r="G174" s="57"/>
@@ -2437,6 +2647,7 @@
       <x:c r="I174"/>
       <x:c r="J174"/>
       <x:c r="K174" s="64"/>
+      <x:c r="L174" s="83"/>
     </x:row>
     <x:row r="175">
       <x:c r="G175" s="57"/>
@@ -2444,6 +2655,7 @@
       <x:c r="I175"/>
       <x:c r="J175"/>
       <x:c r="K175" s="64"/>
+      <x:c r="L175" s="83"/>
     </x:row>
     <x:row r="176">
       <x:c r="G176" s="57"/>
@@ -2451,6 +2663,7 @@
       <x:c r="I176"/>
       <x:c r="J176"/>
       <x:c r="K176" s="64"/>
+      <x:c r="L176" s="83"/>
     </x:row>
     <x:row r="177">
       <x:c r="G177" s="57"/>
@@ -2458,6 +2671,7 @@
       <x:c r="I177"/>
       <x:c r="J177"/>
       <x:c r="K177" s="64"/>
+      <x:c r="L177" s="83"/>
     </x:row>
     <x:row r="178">
       <x:c r="G178" s="57"/>
@@ -2465,6 +2679,7 @@
       <x:c r="I178"/>
       <x:c r="J178"/>
       <x:c r="K178" s="64"/>
+      <x:c r="L178" s="83"/>
     </x:row>
     <x:row r="179">
       <x:c r="G179" s="57"/>
@@ -2472,6 +2687,7 @@
       <x:c r="I179"/>
       <x:c r="J179"/>
       <x:c r="K179" s="64"/>
+      <x:c r="L179" s="83"/>
     </x:row>
     <x:row r="180">
       <x:c r="G180" s="57"/>
@@ -2479,6 +2695,7 @@
       <x:c r="I180"/>
       <x:c r="J180"/>
       <x:c r="K180" s="64"/>
+      <x:c r="L180" s="83"/>
     </x:row>
     <x:row r="181">
       <x:c r="G181" s="57"/>
@@ -2486,6 +2703,7 @@
       <x:c r="I181"/>
       <x:c r="J181"/>
       <x:c r="K181" s="64"/>
+      <x:c r="L181" s="83"/>
     </x:row>
     <x:row r="182">
       <x:c r="G182" s="57"/>
@@ -2493,6 +2711,7 @@
       <x:c r="I182"/>
       <x:c r="J182"/>
       <x:c r="K182" s="64"/>
+      <x:c r="L182" s="83"/>
     </x:row>
     <x:row r="183">
       <x:c r="G183" s="57"/>
@@ -2500,6 +2719,7 @@
       <x:c r="I183"/>
       <x:c r="J183"/>
       <x:c r="K183" s="64"/>
+      <x:c r="L183" s="83"/>
     </x:row>
     <x:row r="184">
       <x:c r="G184" s="57"/>
@@ -2507,6 +2727,7 @@
       <x:c r="I184"/>
       <x:c r="J184"/>
       <x:c r="K184" s="64"/>
+      <x:c r="L184" s="83"/>
     </x:row>
     <x:row r="185">
       <x:c r="G185" s="57"/>
@@ -2514,6 +2735,7 @@
       <x:c r="I185"/>
       <x:c r="J185"/>
       <x:c r="K185" s="64"/>
+      <x:c r="L185" s="83"/>
     </x:row>
     <x:row r="186">
       <x:c r="G186" s="57"/>
@@ -2521,6 +2743,7 @@
       <x:c r="I186"/>
       <x:c r="J186"/>
       <x:c r="K186" s="64"/>
+      <x:c r="L186" s="83"/>
     </x:row>
     <x:row r="187">
       <x:c r="G187" s="57"/>
@@ -2528,6 +2751,7 @@
       <x:c r="I187"/>
       <x:c r="J187"/>
       <x:c r="K187" s="64"/>
+      <x:c r="L187" s="83"/>
     </x:row>
     <x:row r="188">
       <x:c r="G188" s="57"/>
@@ -2535,6 +2759,7 @@
       <x:c r="I188"/>
       <x:c r="J188"/>
       <x:c r="K188" s="64"/>
+      <x:c r="L188" s="83"/>
     </x:row>
     <x:row r="189">
       <x:c r="G189" s="57"/>
@@ -2542,6 +2767,7 @@
       <x:c r="I189"/>
       <x:c r="J189"/>
       <x:c r="K189" s="64"/>
+      <x:c r="L189" s="83"/>
     </x:row>
     <x:row r="190">
       <x:c r="G190" s="57"/>
@@ -2549,6 +2775,7 @@
       <x:c r="I190"/>
       <x:c r="J190"/>
       <x:c r="K190" s="64"/>
+      <x:c r="L190" s="83"/>
     </x:row>
     <x:row r="191">
       <x:c r="G191" s="57"/>
@@ -2556,6 +2783,7 @@
       <x:c r="I191"/>
       <x:c r="J191"/>
       <x:c r="K191" s="64"/>
+      <x:c r="L191" s="83"/>
     </x:row>
     <x:row r="192">
       <x:c r="G192" s="57"/>
@@ -2563,6 +2791,7 @@
       <x:c r="I192"/>
       <x:c r="J192"/>
       <x:c r="K192" s="64"/>
+      <x:c r="L192" s="83"/>
     </x:row>
     <x:row r="193">
       <x:c r="G193" s="57"/>
@@ -2570,6 +2799,7 @@
       <x:c r="I193"/>
       <x:c r="J193"/>
       <x:c r="K193" s="64"/>
+      <x:c r="L193" s="83"/>
     </x:row>
     <x:row r="194">
       <x:c r="G194" s="57"/>
@@ -2577,6 +2807,7 @@
       <x:c r="I194"/>
       <x:c r="J194"/>
       <x:c r="K194" s="64"/>
+      <x:c r="L194" s="83"/>
     </x:row>
     <x:row r="195">
       <x:c r="G195" s="57"/>
@@ -2584,6 +2815,7 @@
       <x:c r="I195"/>
       <x:c r="J195"/>
       <x:c r="K195" s="64"/>
+      <x:c r="L195" s="83"/>
     </x:row>
     <x:row r="196">
       <x:c r="G196" s="57"/>
@@ -2591,6 +2823,7 @@
       <x:c r="I196"/>
       <x:c r="J196"/>
       <x:c r="K196" s="64"/>
+      <x:c r="L196" s="83"/>
     </x:row>
     <x:row r="197">
       <x:c r="G197" s="57"/>
@@ -2598,6 +2831,7 @@
       <x:c r="I197"/>
       <x:c r="J197"/>
       <x:c r="K197" s="64"/>
+      <x:c r="L197" s="83"/>
     </x:row>
     <x:row r="198">
       <x:c r="G198" s="57"/>
@@ -2605,6 +2839,7 @@
       <x:c r="I198"/>
       <x:c r="J198"/>
       <x:c r="K198" s="64"/>
+      <x:c r="L198" s="83"/>
     </x:row>
     <x:row r="199">
       <x:c r="G199" s="57"/>
@@ -2612,6 +2847,7 @@
       <x:c r="I199"/>
       <x:c r="J199"/>
       <x:c r="K199" s="64"/>
+      <x:c r="L199" s="83"/>
     </x:row>
     <x:row r="200">
       <x:c r="G200" s="57"/>
@@ -2619,6 +2855,7 @@
       <x:c r="I200"/>
       <x:c r="J200"/>
       <x:c r="K200" s="64"/>
+      <x:c r="L200" s="83"/>
     </x:row>
     <x:row r="201">
       <x:c r="G201" s="57"/>
@@ -2626,6 +2863,7 @@
       <x:c r="I201"/>
       <x:c r="J201"/>
       <x:c r="K201" s="64"/>
+      <x:c r="L201" s="83"/>
     </x:row>
     <x:row r="202">
       <x:c r="G202" s="57"/>
@@ -2633,6 +2871,7 @@
       <x:c r="I202"/>
       <x:c r="J202"/>
       <x:c r="K202" s="64"/>
+      <x:c r="L202" s="83"/>
     </x:row>
     <x:row r="203">
       <x:c r="G203" s="57"/>
@@ -2640,6 +2879,7 @@
       <x:c r="I203"/>
       <x:c r="J203"/>
       <x:c r="K203" s="64"/>
+      <x:c r="L203" s="83"/>
     </x:row>
     <x:row r="204">
       <x:c r="G204" s="57"/>
@@ -2647,6 +2887,7 @@
       <x:c r="I204"/>
       <x:c r="J204"/>
       <x:c r="K204" s="64"/>
+      <x:c r="L204" s="83"/>
     </x:row>
     <x:row r="205">
       <x:c r="G205" s="57"/>
@@ -2654,6 +2895,7 @@
       <x:c r="I205"/>
       <x:c r="J205"/>
       <x:c r="K205" s="64"/>
+      <x:c r="L205" s="83"/>
     </x:row>
     <x:row r="206">
       <x:c r="G206" s="57"/>
@@ -2661,6 +2903,7 @@
       <x:c r="I206"/>
       <x:c r="J206"/>
       <x:c r="K206" s="64"/>
+      <x:c r="L206" s="83"/>
     </x:row>
     <x:row r="207">
       <x:c r="G207" s="57"/>
@@ -2668,6 +2911,7 @@
       <x:c r="I207"/>
       <x:c r="J207"/>
       <x:c r="K207" s="64"/>
+      <x:c r="L207" s="83"/>
     </x:row>
     <x:row r="208">
       <x:c r="G208" s="57"/>
@@ -2675,6 +2919,7 @@
       <x:c r="I208"/>
       <x:c r="J208"/>
       <x:c r="K208" s="64"/>
+      <x:c r="L208" s="83"/>
     </x:row>
     <x:row r="209">
       <x:c r="G209" s="57"/>
@@ -2682,6 +2927,7 @@
       <x:c r="I209"/>
       <x:c r="J209"/>
       <x:c r="K209" s="64"/>
+      <x:c r="L209" s="83"/>
     </x:row>
     <x:row r="210">
       <x:c r="G210" s="57"/>
@@ -2689,6 +2935,7 @@
       <x:c r="I210"/>
       <x:c r="J210"/>
       <x:c r="K210" s="64"/>
+      <x:c r="L210" s="83"/>
     </x:row>
     <x:row r="211">
       <x:c r="G211" s="57"/>
@@ -2696,6 +2943,7 @@
       <x:c r="I211"/>
       <x:c r="J211"/>
       <x:c r="K211" s="64"/>
+      <x:c r="L211" s="83"/>
     </x:row>
     <x:row r="212">
       <x:c r="G212" s="57"/>
@@ -2703,6 +2951,7 @@
       <x:c r="I212"/>
       <x:c r="J212"/>
       <x:c r="K212" s="64"/>
+      <x:c r="L212" s="83"/>
     </x:row>
     <x:row r="213">
       <x:c r="G213" s="57"/>
@@ -2710,6 +2959,7 @@
       <x:c r="I213"/>
       <x:c r="J213"/>
       <x:c r="K213" s="64"/>
+      <x:c r="L213" s="83"/>
     </x:row>
     <x:row r="214">
       <x:c r="G214" s="57"/>
@@ -2717,6 +2967,7 @@
       <x:c r="I214"/>
       <x:c r="J214"/>
       <x:c r="K214" s="64"/>
+      <x:c r="L214" s="83"/>
     </x:row>
     <x:row r="215">
       <x:c r="G215" s="57"/>
@@ -2724,6 +2975,7 @@
       <x:c r="I215"/>
       <x:c r="J215"/>
       <x:c r="K215" s="64"/>
+      <x:c r="L215" s="83"/>
     </x:row>
     <x:row r="216">
       <x:c r="G216" s="57"/>
@@ -2731,6 +2983,7 @@
       <x:c r="I216"/>
       <x:c r="J216"/>
       <x:c r="K216" s="64"/>
+      <x:c r="L216" s="83"/>
     </x:row>
     <x:row r="217">
       <x:c r="G217" s="57"/>
@@ -2738,6 +2991,7 @@
       <x:c r="I217"/>
       <x:c r="J217"/>
       <x:c r="K217" s="64"/>
+      <x:c r="L217" s="83"/>
     </x:row>
     <x:row r="218">
       <x:c r="G218" s="57"/>
@@ -2745,6 +2999,7 @@
       <x:c r="I218"/>
       <x:c r="J218"/>
       <x:c r="K218" s="64"/>
+      <x:c r="L218" s="83"/>
     </x:row>
     <x:row r="219">
       <x:c r="G219" s="57"/>
@@ -2752,6 +3007,7 @@
       <x:c r="I219"/>
       <x:c r="J219"/>
       <x:c r="K219" s="64"/>
+      <x:c r="L219" s="83"/>
     </x:row>
     <x:row r="220">
       <x:c r="G220" s="57"/>
@@ -2759,6 +3015,7 @@
       <x:c r="I220"/>
       <x:c r="J220"/>
       <x:c r="K220" s="64"/>
+      <x:c r="L220" s="83"/>
     </x:row>
     <x:row r="221">
       <x:c r="G221" s="57"/>
@@ -2766,6 +3023,7 @@
       <x:c r="I221"/>
       <x:c r="J221"/>
       <x:c r="K221" s="64"/>
+      <x:c r="L221" s="83"/>
     </x:row>
     <x:row r="222">
       <x:c r="G222" s="57"/>
@@ -2773,6 +3031,7 @@
       <x:c r="I222"/>
       <x:c r="J222"/>
       <x:c r="K222" s="64"/>
+      <x:c r="L222" s="83"/>
     </x:row>
     <x:row r="223">
       <x:c r="G223" s="57"/>
@@ -2780,6 +3039,7 @@
       <x:c r="I223"/>
       <x:c r="J223"/>
       <x:c r="K223" s="64"/>
+      <x:c r="L223" s="83"/>
     </x:row>
     <x:row r="224">
       <x:c r="G224" s="57"/>
@@ -2787,6 +3047,7 @@
       <x:c r="I224"/>
       <x:c r="J224"/>
       <x:c r="K224" s="64"/>
+      <x:c r="L224" s="83"/>
     </x:row>
     <x:row r="225">
       <x:c r="G225" s="57"/>
@@ -2794,6 +3055,7 @@
       <x:c r="I225"/>
       <x:c r="J225"/>
       <x:c r="K225" s="64"/>
+      <x:c r="L225" s="83"/>
     </x:row>
     <x:row r="226">
       <x:c r="G226" s="57"/>
@@ -2801,6 +3063,7 @@
       <x:c r="I226"/>
       <x:c r="J226"/>
       <x:c r="K226" s="64"/>
+      <x:c r="L226" s="83"/>
     </x:row>
     <x:row r="227">
       <x:c r="G227" s="57"/>
@@ -2808,6 +3071,7 @@
       <x:c r="I227"/>
       <x:c r="J227"/>
       <x:c r="K227" s="64"/>
+      <x:c r="L227" s="83"/>
     </x:row>
     <x:row r="228">
       <x:c r="G228" s="57"/>
@@ -2815,6 +3079,7 @@
       <x:c r="I228"/>
       <x:c r="J228"/>
       <x:c r="K228" s="64"/>
+      <x:c r="L228" s="83"/>
     </x:row>
     <x:row r="229">
       <x:c r="G229" s="57"/>
@@ -2822,6 +3087,7 @@
       <x:c r="I229"/>
       <x:c r="J229"/>
       <x:c r="K229" s="64"/>
+      <x:c r="L229" s="83"/>
     </x:row>
     <x:row r="230">
       <x:c r="G230" s="57"/>
@@ -2829,6 +3095,7 @@
       <x:c r="I230"/>
       <x:c r="J230"/>
       <x:c r="K230" s="64"/>
+      <x:c r="L230" s="83"/>
     </x:row>
     <x:row r="231">
       <x:c r="G231" s="57"/>
@@ -2836,6 +3103,7 @@
       <x:c r="I231"/>
       <x:c r="J231"/>
       <x:c r="K231" s="64"/>
+      <x:c r="L231" s="83"/>
     </x:row>
     <x:row r="232">
       <x:c r="G232" s="57"/>
@@ -2843,6 +3111,7 @@
       <x:c r="I232"/>
       <x:c r="J232"/>
       <x:c r="K232" s="64"/>
+      <x:c r="L232" s="83"/>
     </x:row>
     <x:row r="233">
       <x:c r="G233" s="57"/>
@@ -2850,6 +3119,7 @@
       <x:c r="I233"/>
       <x:c r="J233"/>
       <x:c r="K233" s="64"/>
+      <x:c r="L233" s="83"/>
     </x:row>
     <x:row r="234">
       <x:c r="G234" s="57"/>
@@ -2857,6 +3127,7 @@
       <x:c r="I234"/>
       <x:c r="J234"/>
       <x:c r="K234" s="64"/>
+      <x:c r="L234" s="83"/>
     </x:row>
     <x:row r="235">
       <x:c r="G235" s="57"/>
@@ -2864,6 +3135,7 @@
       <x:c r="I235"/>
       <x:c r="J235"/>
       <x:c r="K235" s="64"/>
+      <x:c r="L235" s="83"/>
     </x:row>
     <x:row r="236">
       <x:c r="G236" s="57"/>
@@ -2871,6 +3143,7 @@
       <x:c r="I236"/>
       <x:c r="J236"/>
       <x:c r="K236" s="64"/>
+      <x:c r="L236" s="83"/>
     </x:row>
     <x:row r="237">
       <x:c r="G237" s="57"/>
@@ -2878,6 +3151,7 @@
       <x:c r="I237"/>
       <x:c r="J237"/>
       <x:c r="K237" s="64"/>
+      <x:c r="L237" s="83"/>
     </x:row>
     <x:row r="238">
       <x:c r="G238" s="57"/>
@@ -2885,6 +3159,7 @@
       <x:c r="I238"/>
       <x:c r="J238"/>
       <x:c r="K238" s="64"/>
+      <x:c r="L238" s="83"/>
     </x:row>
     <x:row r="239">
       <x:c r="G239" s="57"/>
@@ -2892,6 +3167,7 @@
       <x:c r="I239"/>
       <x:c r="J239"/>
       <x:c r="K239" s="64"/>
+      <x:c r="L239" s="83"/>
     </x:row>
     <x:row r="240">
       <x:c r="G240" s="57"/>
@@ -2899,6 +3175,7 @@
       <x:c r="I240"/>
       <x:c r="J240"/>
       <x:c r="K240" s="64"/>
+      <x:c r="L240" s="83"/>
     </x:row>
     <x:row r="241">
       <x:c r="G241" s="57"/>
@@ -2906,6 +3183,7 @@
       <x:c r="I241"/>
       <x:c r="J241"/>
       <x:c r="K241" s="64"/>
+      <x:c r="L241" s="83"/>
     </x:row>
     <x:row r="242">
       <x:c r="G242" s="57"/>
@@ -2913,6 +3191,7 @@
       <x:c r="I242"/>
       <x:c r="J242"/>
       <x:c r="K242" s="64"/>
+      <x:c r="L242" s="83"/>
     </x:row>
     <x:row r="243">
       <x:c r="G243" s="57"/>
@@ -2920,6 +3199,7 @@
       <x:c r="I243"/>
       <x:c r="J243"/>
       <x:c r="K243" s="64"/>
+      <x:c r="L243" s="83"/>
     </x:row>
     <x:row r="244">
       <x:c r="G244" s="57"/>
@@ -2927,6 +3207,7 @@
       <x:c r="I244"/>
       <x:c r="J244"/>
       <x:c r="K244" s="64"/>
+      <x:c r="L244" s="83"/>
     </x:row>
     <x:row r="245">
       <x:c r="G245" s="57"/>
@@ -2934,6 +3215,7 @@
       <x:c r="I245"/>
       <x:c r="J245"/>
       <x:c r="K245" s="64"/>
+      <x:c r="L245" s="83"/>
     </x:row>
     <x:row r="246">
       <x:c r="G246" s="57"/>
@@ -2941,6 +3223,7 @@
       <x:c r="I246"/>
       <x:c r="J246"/>
       <x:c r="K246" s="64"/>
+      <x:c r="L246" s="83"/>
     </x:row>
     <x:row r="247">
       <x:c r="G247" s="57"/>
@@ -2948,6 +3231,7 @@
       <x:c r="I247"/>
       <x:c r="J247"/>
       <x:c r="K247" s="64"/>
+      <x:c r="L247" s="83"/>
     </x:row>
     <x:row r="248">
       <x:c r="G248" s="57"/>
@@ -2955,6 +3239,7 @@
       <x:c r="I248"/>
       <x:c r="J248"/>
       <x:c r="K248" s="64"/>
+      <x:c r="L248" s="83"/>
     </x:row>
     <x:row r="249">
       <x:c r="G249" s="57"/>
@@ -2962,6 +3247,7 @@
       <x:c r="I249"/>
       <x:c r="J249"/>
       <x:c r="K249" s="64"/>
+      <x:c r="L249" s="83"/>
     </x:row>
     <x:row r="250">
       <x:c r="G250" s="57"/>
@@ -2969,6 +3255,7 @@
       <x:c r="I250"/>
       <x:c r="J250"/>
       <x:c r="K250" s="64"/>
+      <x:c r="L250" s="83"/>
     </x:row>
     <x:row r="251">
       <x:c r="G251" s="57"/>
@@ -2976,6 +3263,7 @@
       <x:c r="I251"/>
       <x:c r="J251"/>
       <x:c r="K251" s="64"/>
+      <x:c r="L251" s="83"/>
     </x:row>
     <x:row r="252">
       <x:c r="G252" s="57"/>
@@ -2983,6 +3271,7 @@
       <x:c r="I252"/>
       <x:c r="J252"/>
       <x:c r="K252" s="64"/>
+      <x:c r="L252" s="83"/>
     </x:row>
     <x:row r="253">
       <x:c r="G253" s="57"/>
@@ -2990,6 +3279,7 @@
       <x:c r="I253"/>
       <x:c r="J253"/>
       <x:c r="K253" s="64"/>
+      <x:c r="L253" s="83"/>
     </x:row>
     <x:row r="254">
       <x:c r="G254" s="57"/>
@@ -2997,6 +3287,7 @@
       <x:c r="I254"/>
       <x:c r="J254"/>
       <x:c r="K254" s="64"/>
+      <x:c r="L254" s="83"/>
     </x:row>
     <x:row r="255">
       <x:c r="G255" s="57"/>
@@ -3004,6 +3295,7 @@
       <x:c r="I255"/>
       <x:c r="J255"/>
       <x:c r="K255" s="64"/>
+      <x:c r="L255" s="83"/>
     </x:row>
     <x:row r="256">
       <x:c r="G256" s="57"/>
@@ -3011,6 +3303,7 @@
       <x:c r="I256"/>
       <x:c r="J256"/>
       <x:c r="K256" s="64"/>
+      <x:c r="L256" s="83"/>
     </x:row>
     <x:row r="257">
       <x:c r="G257" s="57"/>
@@ -3018,6 +3311,7 @@
       <x:c r="I257"/>
       <x:c r="J257"/>
       <x:c r="K257" s="64"/>
+      <x:c r="L257" s="83"/>
     </x:row>
     <x:row r="258">
       <x:c r="G258" s="57"/>
@@ -3025,6 +3319,7 @@
       <x:c r="I258"/>
       <x:c r="J258"/>
       <x:c r="K258" s="64"/>
+      <x:c r="L258" s="83"/>
     </x:row>
     <x:row r="259">
       <x:c r="G259" s="57"/>
@@ -3032,6 +3327,7 @@
       <x:c r="I259"/>
       <x:c r="J259"/>
       <x:c r="K259" s="64"/>
+      <x:c r="L259" s="83"/>
     </x:row>
     <x:row r="260">
       <x:c r="G260" s="57"/>
@@ -3039,6 +3335,7 @@
       <x:c r="I260"/>
       <x:c r="J260"/>
       <x:c r="K260" s="64"/>
+      <x:c r="L260" s="83"/>
     </x:row>
     <x:row r="261">
       <x:c r="G261" s="57"/>
@@ -3046,6 +3343,7 @@
       <x:c r="I261"/>
       <x:c r="J261"/>
       <x:c r="K261" s="64"/>
+      <x:c r="L261" s="83"/>
     </x:row>
     <x:row r="262">
       <x:c r="G262" s="57"/>
@@ -3053,6 +3351,7 @@
       <x:c r="I262"/>
       <x:c r="J262"/>
       <x:c r="K262" s="64"/>
+      <x:c r="L262" s="83"/>
     </x:row>
     <x:row r="263">
       <x:c r="G263" s="57"/>
@@ -3060,6 +3359,7 @@
       <x:c r="I263"/>
       <x:c r="J263"/>
       <x:c r="K263" s="64"/>
+      <x:c r="L263" s="83"/>
     </x:row>
     <x:row r="264">
       <x:c r="G264" s="57"/>
@@ -3067,6 +3367,7 @@
       <x:c r="I264"/>
       <x:c r="J264"/>
       <x:c r="K264" s="64"/>
+      <x:c r="L264" s="83"/>
     </x:row>
     <x:row r="265">
       <x:c r="G265" s="57"/>
@@ -3074,6 +3375,7 @@
       <x:c r="I265"/>
       <x:c r="J265"/>
       <x:c r="K265" s="64"/>
+      <x:c r="L265" s="83"/>
     </x:row>
     <x:row r="266">
       <x:c r="G266" s="57"/>
@@ -3081,6 +3383,7 @@
       <x:c r="I266"/>
       <x:c r="J266"/>
       <x:c r="K266" s="64"/>
+      <x:c r="L266" s="83"/>
     </x:row>
     <x:row r="267">
       <x:c r="G267" s="57"/>
@@ -3088,6 +3391,7 @@
       <x:c r="I267"/>
       <x:c r="J267"/>
       <x:c r="K267" s="64"/>
+      <x:c r="L267" s="83"/>
     </x:row>
     <x:row r="268">
       <x:c r="G268" s="57"/>
@@ -3095,6 +3399,7 @@
       <x:c r="I268"/>
       <x:c r="J268"/>
       <x:c r="K268" s="64"/>
+      <x:c r="L268" s="83"/>
     </x:row>
     <x:row r="269">
       <x:c r="G269" s="57"/>
@@ -3102,6 +3407,7 @@
       <x:c r="I269"/>
       <x:c r="J269"/>
       <x:c r="K269" s="64"/>
+      <x:c r="L269" s="83"/>
     </x:row>
     <x:row r="270">
       <x:c r="G270" s="57"/>
@@ -3109,6 +3415,7 @@
       <x:c r="I270"/>
       <x:c r="J270"/>
       <x:c r="K270" s="64"/>
+      <x:c r="L270" s="83"/>
     </x:row>
     <x:row r="271">
       <x:c r="G271" s="57"/>
@@ -3116,6 +3423,7 @@
       <x:c r="I271"/>
       <x:c r="J271"/>
       <x:c r="K271" s="64"/>
+      <x:c r="L271" s="83"/>
     </x:row>
     <x:row r="272">
       <x:c r="G272" s="57"/>
@@ -3123,6 +3431,7 @@
       <x:c r="I272"/>
       <x:c r="J272"/>
       <x:c r="K272" s="64"/>
+      <x:c r="L272" s="83"/>
     </x:row>
     <x:row r="273">
       <x:c r="G273" s="57"/>
@@ -3130,6 +3439,7 @@
       <x:c r="I273"/>
       <x:c r="J273"/>
       <x:c r="K273" s="64"/>
+      <x:c r="L273" s="83"/>
     </x:row>
     <x:row r="274">
       <x:c r="G274" s="57"/>
@@ -3137,6 +3447,7 @@
       <x:c r="I274"/>
       <x:c r="J274"/>
       <x:c r="K274" s="64"/>
+      <x:c r="L274" s="83"/>
     </x:row>
     <x:row r="275">
       <x:c r="G275" s="57"/>
@@ -3144,6 +3455,7 @@
       <x:c r="I275"/>
       <x:c r="J275"/>
       <x:c r="K275" s="64"/>
+      <x:c r="L275" s="83"/>
     </x:row>
     <x:row r="276">
       <x:c r="G276" s="57"/>
@@ -3151,6 +3463,7 @@
       <x:c r="I276"/>
       <x:c r="J276"/>
       <x:c r="K276" s="64"/>
+      <x:c r="L276" s="83"/>
     </x:row>
     <x:row r="277">
       <x:c r="G277" s="57"/>
@@ -3158,6 +3471,7 @@
       <x:c r="I277"/>
       <x:c r="J277"/>
       <x:c r="K277" s="64"/>
+      <x:c r="L277" s="83"/>
     </x:row>
     <x:row r="278">
       <x:c r="G278" s="57"/>
@@ -3165,6 +3479,7 @@
       <x:c r="I278"/>
       <x:c r="J278"/>
       <x:c r="K278" s="64"/>
+      <x:c r="L278" s="83"/>
     </x:row>
     <x:row r="279">
       <x:c r="G279" s="57"/>
@@ -3172,6 +3487,7 @@
       <x:c r="I279"/>
       <x:c r="J279"/>
       <x:c r="K279" s="64"/>
+      <x:c r="L279" s="83"/>
     </x:row>
     <x:row r="280">
       <x:c r="G280" s="57"/>
@@ -3179,6 +3495,7 @@
       <x:c r="I280"/>
       <x:c r="J280"/>
       <x:c r="K280" s="64"/>
+      <x:c r="L280" s="83"/>
     </x:row>
     <x:row r="281">
       <x:c r="G281" s="57"/>
@@ -3186,6 +3503,7 @@
       <x:c r="I281"/>
       <x:c r="J281"/>
       <x:c r="K281" s="64"/>
+      <x:c r="L281" s="83"/>
     </x:row>
     <x:row r="282">
       <x:c r="G282" s="57"/>
@@ -3193,6 +3511,7 @@
       <x:c r="I282"/>
       <x:c r="J282"/>
       <x:c r="K282" s="64"/>
+      <x:c r="L282" s="83"/>
     </x:row>
     <x:row r="283">
       <x:c r="G283" s="57"/>
@@ -3200,6 +3519,7 @@
       <x:c r="I283"/>
       <x:c r="J283"/>
       <x:c r="K283" s="64"/>
+      <x:c r="L283" s="83"/>
     </x:row>
     <x:row r="284">
       <x:c r="G284" s="57"/>
@@ -3207,6 +3527,7 @@
       <x:c r="I284"/>
       <x:c r="J284"/>
       <x:c r="K284" s="64"/>
+      <x:c r="L284" s="83"/>
     </x:row>
     <x:row r="285">
       <x:c r="G285" s="57"/>
@@ -3214,6 +3535,7 @@
       <x:c r="I285"/>
       <x:c r="J285"/>
       <x:c r="K285" s="64"/>
+      <x:c r="L285" s="83"/>
     </x:row>
     <x:row r="286">
       <x:c r="G286" s="57"/>
@@ -3221,6 +3543,7 @@
       <x:c r="I286"/>
       <x:c r="J286"/>
       <x:c r="K286" s="64"/>
+      <x:c r="L286" s="83"/>
     </x:row>
     <x:row r="287">
       <x:c r="G287" s="57"/>
@@ -3228,6 +3551,7 @@
       <x:c r="I287"/>
       <x:c r="J287"/>
       <x:c r="K287" s="64"/>
+      <x:c r="L287" s="83"/>
     </x:row>
     <x:row r="288">
       <x:c r="G288" s="57"/>
@@ -3235,6 +3559,7 @@
       <x:c r="I288"/>
       <x:c r="J288"/>
       <x:c r="K288" s="64"/>
+      <x:c r="L288" s="83"/>
     </x:row>
     <x:row r="289">
       <x:c r="G289" s="57"/>
@@ -3242,6 +3567,7 @@
       <x:c r="I289"/>
       <x:c r="J289"/>
       <x:c r="K289" s="64"/>
+      <x:c r="L289" s="83"/>
     </x:row>
     <x:row r="290">
       <x:c r="G290" s="57"/>
@@ -3249,6 +3575,7 @@
       <x:c r="I290"/>
       <x:c r="J290"/>
       <x:c r="K290" s="64"/>
+      <x:c r="L290" s="83"/>
     </x:row>
     <x:row r="291">
       <x:c r="G291" s="57"/>
@@ -3256,6 +3583,7 @@
       <x:c r="I291"/>
       <x:c r="J291"/>
       <x:c r="K291" s="64"/>
+      <x:c r="L291" s="83"/>
     </x:row>
     <x:row r="292">
       <x:c r="G292" s="57"/>
@@ -3263,6 +3591,7 @@
       <x:c r="I292"/>
       <x:c r="J292"/>
       <x:c r="K292" s="64"/>
+      <x:c r="L292" s="83"/>
     </x:row>
     <x:row r="293">
       <x:c r="G293" s="57"/>
@@ -3270,6 +3599,7 @@
       <x:c r="I293"/>
       <x:c r="J293"/>
       <x:c r="K293" s="64"/>
+      <x:c r="L293" s="83"/>
     </x:row>
     <x:row r="294">
       <x:c r="G294" s="57"/>
@@ -3277,6 +3607,7 @@
       <x:c r="I294"/>
       <x:c r="J294"/>
       <x:c r="K294" s="64"/>
+      <x:c r="L294" s="83"/>
     </x:row>
     <x:row r="295">
       <x:c r="G295" s="57"/>
@@ -3284,6 +3615,7 @@
       <x:c r="I295"/>
       <x:c r="J295"/>
       <x:c r="K295" s="64"/>
+      <x:c r="L295" s="83"/>
     </x:row>
     <x:row r="296">
       <x:c r="G296" s="57"/>
@@ -3291,6 +3623,7 @@
       <x:c r="I296"/>
       <x:c r="J296"/>
       <x:c r="K296" s="64"/>
+      <x:c r="L296" s="83"/>
     </x:row>
     <x:row r="297">
       <x:c r="G297" s="57"/>
@@ -3298,6 +3631,7 @@
       <x:c r="I297"/>
       <x:c r="J297"/>
       <x:c r="K297" s="64"/>
+      <x:c r="L297" s="83"/>
     </x:row>
     <x:row r="298">
       <x:c r="G298" s="57"/>
@@ -3305,6 +3639,7 @@
       <x:c r="I298"/>
       <x:c r="J298"/>
       <x:c r="K298" s="64"/>
+      <x:c r="L298" s="83"/>
     </x:row>
     <x:row r="299">
       <x:c r="G299" s="57"/>
@@ -3312,6 +3647,7 @@
       <x:c r="I299"/>
       <x:c r="J299"/>
       <x:c r="K299" s="64"/>
+      <x:c r="L299" s="83"/>
     </x:row>
     <x:row r="300">
       <x:c r="G300" s="57"/>
@@ -3319,6 +3655,7 @@
       <x:c r="I300"/>
       <x:c r="J300"/>
       <x:c r="K300" s="64"/>
+      <x:c r="L300" s="83"/>
     </x:row>
     <x:row r="301">
       <x:c r="G301" s="57"/>
@@ -3326,6 +3663,7 @@
       <x:c r="I301"/>
       <x:c r="J301"/>
       <x:c r="K301" s="64"/>
+      <x:c r="L301" s="83"/>
     </x:row>
     <x:row r="302">
       <x:c r="G302" s="57"/>
@@ -3333,6 +3671,7 @@
       <x:c r="I302"/>
       <x:c r="J302"/>
       <x:c r="K302" s="64"/>
+      <x:c r="L302" s="83"/>
     </x:row>
     <x:row r="303">
       <x:c r="G303" s="57"/>
@@ -3340,6 +3679,7 @@
       <x:c r="I303"/>
       <x:c r="J303"/>
       <x:c r="K303" s="64"/>
+      <x:c r="L303" s="83"/>
     </x:row>
     <x:row r="304">
       <x:c r="G304" s="57"/>
@@ -3347,6 +3687,7 @@
       <x:c r="I304"/>
       <x:c r="J304"/>
       <x:c r="K304" s="64"/>
+      <x:c r="L304" s="83"/>
     </x:row>
     <x:row r="305">
       <x:c r="G305" s="57"/>
@@ -3354,6 +3695,7 @@
       <x:c r="I305"/>
       <x:c r="J305"/>
       <x:c r="K305" s="64"/>
+      <x:c r="L305" s="83"/>
     </x:row>
     <x:row r="306">
       <x:c r="G306" s="57"/>
@@ -3361,6 +3703,7 @@
       <x:c r="I306"/>
       <x:c r="J306"/>
       <x:c r="K306" s="64"/>
+      <x:c r="L306" s="83"/>
     </x:row>
     <x:row r="307">
       <x:c r="G307" s="57"/>
@@ -3368,6 +3711,7 @@
       <x:c r="I307"/>
       <x:c r="J307"/>
       <x:c r="K307" s="64"/>
+      <x:c r="L307" s="83"/>
     </x:row>
     <x:row r="308">
       <x:c r="G308" s="57"/>
@@ -3375,6 +3719,7 @@
       <x:c r="I308"/>
       <x:c r="J308"/>
       <x:c r="K308" s="64"/>
+      <x:c r="L308" s="83"/>
     </x:row>
     <x:row r="309">
       <x:c r="G309" s="57"/>
@@ -3382,6 +3727,7 @@
       <x:c r="I309"/>
       <x:c r="J309"/>
       <x:c r="K309" s="64"/>
+      <x:c r="L309" s="83"/>
     </x:row>
     <x:row r="310">
       <x:c r="G310" s="57"/>
@@ -3389,6 +3735,7 @@
       <x:c r="I310"/>
       <x:c r="J310"/>
       <x:c r="K310" s="64"/>
+      <x:c r="L310" s="83"/>
     </x:row>
     <x:row r="311">
       <x:c r="G311" s="57"/>
@@ -3396,6 +3743,7 @@
       <x:c r="I311"/>
       <x:c r="J311"/>
       <x:c r="K311" s="64"/>
+      <x:c r="L311" s="83"/>
     </x:row>
     <x:row r="312">
       <x:c r="G312" s="57"/>
@@ -3403,6 +3751,7 @@
       <x:c r="I312"/>
       <x:c r="J312"/>
       <x:c r="K312" s="64"/>
+      <x:c r="L312" s="83"/>
     </x:row>
     <x:row r="313">
       <x:c r="G313" s="57"/>
@@ -3410,6 +3759,7 @@
       <x:c r="I313"/>
       <x:c r="J313"/>
       <x:c r="K313" s="64"/>
+      <x:c r="L313" s="83"/>
     </x:row>
     <x:row r="314">
       <x:c r="G314" s="57"/>
@@ -3417,6 +3767,7 @@
       <x:c r="I314"/>
       <x:c r="J314"/>
       <x:c r="K314" s="64"/>
+      <x:c r="L314" s="83"/>
     </x:row>
     <x:row r="315">
       <x:c r="G315" s="57"/>
@@ -3424,6 +3775,7 @@
       <x:c r="I315"/>
       <x:c r="J315"/>
       <x:c r="K315" s="64"/>
+      <x:c r="L315" s="83"/>
     </x:row>
     <x:row r="316">
       <x:c r="G316" s="57"/>
@@ -3431,6 +3783,7 @@
       <x:c r="I316"/>
       <x:c r="J316"/>
       <x:c r="K316" s="64"/>
+      <x:c r="L316" s="83"/>
     </x:row>
     <x:row r="317">
       <x:c r="G317" s="57"/>
@@ -3438,6 +3791,7 @@
       <x:c r="I317"/>
       <x:c r="J317"/>
       <x:c r="K317" s="64"/>
+      <x:c r="L317" s="83"/>
     </x:row>
     <x:row r="318">
       <x:c r="G318" s="57"/>
@@ -3445,6 +3799,7 @@
       <x:c r="I318"/>
       <x:c r="J318"/>
       <x:c r="K318" s="64"/>
+      <x:c r="L318" s="83"/>
     </x:row>
     <x:row r="319">
       <x:c r="G319" s="57"/>
@@ -3452,6 +3807,7 @@
       <x:c r="I319"/>
       <x:c r="J319"/>
       <x:c r="K319" s="64"/>
+      <x:c r="L319" s="83"/>
     </x:row>
     <x:row r="320">
       <x:c r="G320" s="57"/>
@@ -3459,6 +3815,7 @@
       <x:c r="I320"/>
       <x:c r="J320"/>
       <x:c r="K320" s="64"/>
+      <x:c r="L320" s="83"/>
     </x:row>
     <x:row r="321">
       <x:c r="G321" s="57"/>
@@ -3466,6 +3823,7 @@
       <x:c r="I321"/>
       <x:c r="J321"/>
       <x:c r="K321" s="64"/>
+      <x:c r="L321" s="83"/>
     </x:row>
     <x:row r="322">
       <x:c r="G322" s="57"/>
@@ -3473,6 +3831,7 @@
       <x:c r="I322"/>
       <x:c r="J322"/>
       <x:c r="K322" s="64"/>
+      <x:c r="L322" s="83"/>
     </x:row>
     <x:row r="323">
       <x:c r="G323" s="57"/>
@@ -3480,6 +3839,7 @@
       <x:c r="I323"/>
       <x:c r="J323"/>
       <x:c r="K323" s="64"/>
+      <x:c r="L323" s="83"/>
     </x:row>
     <x:row r="324">
       <x:c r="G324" s="57"/>
@@ -3487,6 +3847,7 @@
       <x:c r="I324"/>
       <x:c r="J324"/>
       <x:c r="K324" s="64"/>
+      <x:c r="L324" s="83"/>
     </x:row>
     <x:row r="325">
       <x:c r="G325" s="57"/>
@@ -3494,6 +3855,7 @@
       <x:c r="I325"/>
       <x:c r="J325"/>
       <x:c r="K325" s="64"/>
+      <x:c r="L325" s="83"/>
     </x:row>
     <x:row r="326">
       <x:c r="G326" s="57"/>
@@ -3501,6 +3863,7 @@
       <x:c r="I326"/>
       <x:c r="J326"/>
       <x:c r="K326" s="64"/>
+      <x:c r="L326" s="83"/>
     </x:row>
     <x:row r="327">
       <x:c r="G327" s="57"/>
@@ -3508,6 +3871,7 @@
       <x:c r="I327"/>
       <x:c r="J327"/>
       <x:c r="K327" s="64"/>
+      <x:c r="L327" s="83"/>
     </x:row>
     <x:row r="328">
       <x:c r="G328" s="57"/>
@@ -3515,6 +3879,7 @@
       <x:c r="I328"/>
       <x:c r="J328"/>
       <x:c r="K328" s="64"/>
+      <x:c r="L328" s="83"/>
     </x:row>
     <x:row r="329">
       <x:c r="G329" s="57"/>
@@ -3522,6 +3887,7 @@
       <x:c r="I329"/>
       <x:c r="J329"/>
       <x:c r="K329" s="64"/>
+      <x:c r="L329" s="83"/>
     </x:row>
     <x:row r="330">
       <x:c r="G330" s="57"/>
@@ -3529,6 +3895,7 @@
       <x:c r="I330"/>
       <x:c r="J330"/>
       <x:c r="K330" s="64"/>
+      <x:c r="L330" s="83"/>
     </x:row>
     <x:row r="331">
       <x:c r="G331" s="57"/>
@@ -3536,6 +3903,7 @@
       <x:c r="I331"/>
       <x:c r="J331"/>
       <x:c r="K331" s="64"/>
+      <x:c r="L331" s="83"/>
     </x:row>
     <x:row r="332">
       <x:c r="G332" s="57"/>
@@ -3543,6 +3911,7 @@
       <x:c r="I332"/>
       <x:c r="J332"/>
       <x:c r="K332" s="64"/>
+      <x:c r="L332" s="83"/>
     </x:row>
     <x:row r="333">
       <x:c r="G333" s="57"/>
@@ -3550,6 +3919,7 @@
       <x:c r="I333"/>
       <x:c r="J333"/>
       <x:c r="K333" s="64"/>
+      <x:c r="L333" s="83"/>
     </x:row>
     <x:row r="334">
       <x:c r="G334" s="57"/>
@@ -3557,6 +3927,7 @@
       <x:c r="I334"/>
       <x:c r="J334"/>
       <x:c r="K334" s="64"/>
+      <x:c r="L334" s="83"/>
     </x:row>
     <x:row r="335">
       <x:c r="G335" s="57"/>
@@ -3564,6 +3935,7 @@
       <x:c r="I335"/>
       <x:c r="J335"/>
       <x:c r="K335" s="64"/>
+      <x:c r="L335" s="83"/>
     </x:row>
     <x:row r="336">
       <x:c r="G336" s="57"/>
@@ -3571,6 +3943,7 @@
       <x:c r="I336"/>
       <x:c r="J336"/>
       <x:c r="K336" s="64"/>
+      <x:c r="L336" s="83"/>
     </x:row>
     <x:row r="337">
       <x:c r="G337" s="57"/>
@@ -3578,6 +3951,7 @@
       <x:c r="I337"/>
       <x:c r="J337"/>
       <x:c r="K337" s="64"/>
+      <x:c r="L337" s="83"/>
     </x:row>
     <x:row r="338">
       <x:c r="G338" s="57"/>
@@ -3585,6 +3959,7 @@
       <x:c r="I338"/>
       <x:c r="J338"/>
       <x:c r="K338" s="64"/>
+      <x:c r="L338" s="83"/>
     </x:row>
     <x:row r="339">
       <x:c r="G339" s="57"/>
@@ -3592,6 +3967,7 @@
       <x:c r="I339"/>
       <x:c r="J339"/>
       <x:c r="K339" s="64"/>
+      <x:c r="L339" s="83"/>
     </x:row>
     <x:row r="340">
       <x:c r="G340" s="57"/>
@@ -3599,6 +3975,7 @@
       <x:c r="I340"/>
       <x:c r="J340"/>
       <x:c r="K340" s="64"/>
+      <x:c r="L340" s="83"/>
     </x:row>
     <x:row r="341">
       <x:c r="G341" s="57"/>
@@ -3606,6 +3983,7 @@
       <x:c r="I341"/>
       <x:c r="J341"/>
       <x:c r="K341" s="64"/>
+      <x:c r="L341" s="83"/>
     </x:row>
     <x:row r="342">
       <x:c r="G342" s="57"/>
@@ -3613,6 +3991,7 @@
       <x:c r="I342"/>
       <x:c r="J342"/>
       <x:c r="K342" s="64"/>
+      <x:c r="L342" s="83"/>
     </x:row>
     <x:row r="343">
       <x:c r="G343" s="57"/>
@@ -3620,6 +3999,7 @@
       <x:c r="I343"/>
       <x:c r="J343"/>
       <x:c r="K343" s="64"/>
+      <x:c r="L343" s="83"/>
     </x:row>
     <x:row r="344">
       <x:c r="G344" s="57"/>
@@ -3627,6 +4007,7 @@
       <x:c r="I344"/>
       <x:c r="J344"/>
       <x:c r="K344" s="64"/>
+      <x:c r="L344" s="83"/>
     </x:row>
     <x:row r="345">
       <x:c r="G345" s="57"/>
@@ -3634,6 +4015,7 @@
       <x:c r="I345"/>
       <x:c r="J345"/>
       <x:c r="K345" s="64"/>
+      <x:c r="L345" s="83"/>
     </x:row>
     <x:row r="346">
       <x:c r="G346" s="57"/>
@@ -3641,6 +4023,7 @@
       <x:c r="I346"/>
       <x:c r="J346"/>
       <x:c r="K346" s="64"/>
+      <x:c r="L346" s="83"/>
     </x:row>
     <x:row r="347">
       <x:c r="G347" s="57"/>
@@ -3648,6 +4031,7 @@
       <x:c r="I347"/>
       <x:c r="J347"/>
       <x:c r="K347" s="64"/>
+      <x:c r="L347" s="83"/>
     </x:row>
     <x:row r="348">
       <x:c r="G348" s="57"/>
@@ -3655,6 +4039,7 @@
       <x:c r="I348"/>
       <x:c r="J348"/>
       <x:c r="K348" s="64"/>
+      <x:c r="L348" s="83"/>
     </x:row>
     <x:row r="349">
       <x:c r="G349" s="57"/>
@@ -3662,6 +4047,7 @@
       <x:c r="I349"/>
       <x:c r="J349"/>
       <x:c r="K349" s="64"/>
+      <x:c r="L349" s="83"/>
     </x:row>
     <x:row r="350">
       <x:c r="G350" s="57"/>
@@ -3669,6 +4055,7 @@
       <x:c r="I350"/>
       <x:c r="J350"/>
       <x:c r="K350" s="64"/>
+      <x:c r="L350" s="83"/>
     </x:row>
     <x:row r="351">
       <x:c r="G351" s="57"/>
@@ -3676,6 +4063,7 @@
       <x:c r="I351"/>
       <x:c r="J351"/>
       <x:c r="K351" s="64"/>
+      <x:c r="L351" s="83"/>
     </x:row>
     <x:row r="352">
       <x:c r="G352" s="57"/>
@@ -3683,6 +4071,7 @@
       <x:c r="I352"/>
       <x:c r="J352"/>
       <x:c r="K352" s="64"/>
+      <x:c r="L352" s="83"/>
     </x:row>
     <x:row r="353">
       <x:c r="G353" s="57"/>
@@ -3690,6 +4079,7 @@
       <x:c r="I353"/>
       <x:c r="J353"/>
       <x:c r="K353" s="64"/>
+      <x:c r="L353" s="83"/>
     </x:row>
     <x:row r="354">
       <x:c r="G354" s="57"/>
@@ -3697,6 +4087,7 @@
       <x:c r="I354"/>
       <x:c r="J354"/>
       <x:c r="K354" s="64"/>
+      <x:c r="L354" s="83"/>
     </x:row>
     <x:row r="355">
       <x:c r="G355" s="57"/>
@@ -3704,6 +4095,7 @@
       <x:c r="I355"/>
       <x:c r="J355"/>
       <x:c r="K355" s="64"/>
+      <x:c r="L355" s="83"/>
     </x:row>
     <x:row r="356">
       <x:c r="G356" s="57"/>
@@ -3711,6 +4103,7 @@
       <x:c r="I356"/>
       <x:c r="J356"/>
       <x:c r="K356" s="64"/>
+      <x:c r="L356" s="83"/>
     </x:row>
     <x:row r="357">
       <x:c r="G357" s="57"/>
@@ -3718,6 +4111,7 @@
       <x:c r="I357"/>
       <x:c r="J357"/>
       <x:c r="K357" s="64"/>
+      <x:c r="L357" s="83"/>
     </x:row>
     <x:row r="358">
       <x:c r="G358" s="57"/>
@@ -3725,6 +4119,7 @@
       <x:c r="I358"/>
       <x:c r="J358"/>
       <x:c r="K358" s="64"/>
+      <x:c r="L358" s="83"/>
     </x:row>
     <x:row r="359">
       <x:c r="G359" s="57"/>
@@ -3732,6 +4127,7 @@
       <x:c r="I359"/>
       <x:c r="J359"/>
       <x:c r="K359" s="64"/>
+      <x:c r="L359" s="83"/>
     </x:row>
     <x:row r="360">
       <x:c r="G360" s="57"/>
@@ -3739,6 +4135,7 @@
       <x:c r="I360"/>
       <x:c r="J360"/>
       <x:c r="K360" s="64"/>
+      <x:c r="L360" s="83"/>
     </x:row>
     <x:row r="361">
       <x:c r="G361" s="57"/>
@@ -3746,6 +4143,7 @@
       <x:c r="I361"/>
       <x:c r="J361"/>
       <x:c r="K361" s="64"/>
+      <x:c r="L361" s="83"/>
     </x:row>
     <x:row r="362">
       <x:c r="G362" s="57"/>
@@ -3753,6 +4151,7 @@
       <x:c r="I362"/>
       <x:c r="J362"/>
       <x:c r="K362" s="64"/>
+      <x:c r="L362" s="83"/>
     </x:row>
     <x:row r="363">
       <x:c r="G363" s="57"/>
@@ -3760,6 +4159,7 @@
       <x:c r="I363"/>
       <x:c r="J363"/>
       <x:c r="K363" s="64"/>
+      <x:c r="L363" s="83"/>
     </x:row>
     <x:row r="364">
       <x:c r="G364" s="57"/>
@@ -3767,6 +4167,7 @@
       <x:c r="I364"/>
       <x:c r="J364"/>
       <x:c r="K364" s="64"/>
+      <x:c r="L364" s="83"/>
     </x:row>
     <x:row r="365">
       <x:c r="G365" s="57"/>
@@ -3774,6 +4175,7 @@
       <x:c r="I365"/>
       <x:c r="J365"/>
       <x:c r="K365" s="64"/>
+      <x:c r="L365" s="83"/>
     </x:row>
     <x:row r="366">
       <x:c r="G366" s="57"/>
@@ -3781,6 +4183,7 @@
       <x:c r="I366"/>
       <x:c r="J366"/>
       <x:c r="K366" s="64"/>
+      <x:c r="L366" s="83"/>
     </x:row>
     <x:row r="367">
       <x:c r="G367" s="57"/>
@@ -3788,6 +4191,7 @@
       <x:c r="I367"/>
       <x:c r="J367"/>
       <x:c r="K367" s="64"/>
+      <x:c r="L367" s="83"/>
     </x:row>
     <x:row r="368">
       <x:c r="G368" s="57"/>
@@ -3795,6 +4199,7 @@
       <x:c r="I368"/>
       <x:c r="J368"/>
       <x:c r="K368" s="64"/>
+      <x:c r="L368" s="83"/>
     </x:row>
     <x:row r="369">
       <x:c r="G369" s="57"/>
@@ -3802,6 +4207,7 @@
       <x:c r="I369"/>
       <x:c r="J369"/>
       <x:c r="K369" s="64"/>
+      <x:c r="L369" s="83"/>
     </x:row>
     <x:row r="370">
       <x:c r="G370" s="57"/>
@@ -3809,6 +4215,7 @@
       <x:c r="I370"/>
       <x:c r="J370"/>
       <x:c r="K370" s="64"/>
+      <x:c r="L370" s="83"/>
     </x:row>
     <x:row r="371">
       <x:c r="G371" s="57"/>
@@ -3816,6 +4223,7 @@
       <x:c r="I371"/>
       <x:c r="J371"/>
       <x:c r="K371" s="64"/>
+      <x:c r="L371" s="83"/>
     </x:row>
     <x:row r="372">
       <x:c r="G372" s="57"/>
@@ -3823,6 +4231,7 @@
       <x:c r="I372"/>
       <x:c r="J372"/>
       <x:c r="K372" s="64"/>
+      <x:c r="L372" s="83"/>
     </x:row>
     <x:row r="373">
       <x:c r="G373" s="57"/>
@@ -3830,6 +4239,7 @@
       <x:c r="I373"/>
       <x:c r="J373"/>
       <x:c r="K373" s="64"/>
+      <x:c r="L373" s="83"/>
     </x:row>
     <x:row r="374">
       <x:c r="G374" s="57"/>
@@ -3837,6 +4247,7 @@
       <x:c r="I374"/>
       <x:c r="J374"/>
       <x:c r="K374" s="64"/>
+      <x:c r="L374" s="83"/>
     </x:row>
     <x:row r="375">
       <x:c r="G375" s="57"/>
@@ -3844,6 +4255,7 @@
       <x:c r="I375"/>
       <x:c r="J375"/>
       <x:c r="K375" s="64"/>
+      <x:c r="L375" s="83"/>
     </x:row>
     <x:row r="376">
       <x:c r="G376" s="57"/>
@@ -3851,6 +4263,7 @@
       <x:c r="I376"/>
       <x:c r="J376"/>
       <x:c r="K376" s="64"/>
+      <x:c r="L376" s="83"/>
     </x:row>
     <x:row r="377">
       <x:c r="G377" s="57"/>
@@ -3858,6 +4271,7 @@
       <x:c r="I377"/>
       <x:c r="J377"/>
       <x:c r="K377" s="64"/>
+      <x:c r="L377" s="83"/>
     </x:row>
     <x:row r="378">
       <x:c r="G378" s="57"/>
@@ -3865,6 +4279,7 @@
       <x:c r="I378"/>
       <x:c r="J378"/>
       <x:c r="K378" s="64"/>
+      <x:c r="L378" s="83"/>
     </x:row>
     <x:row r="379">
       <x:c r="G379" s="57"/>
@@ -3872,6 +4287,7 @@
       <x:c r="I379"/>
       <x:c r="J379"/>
       <x:c r="K379" s="64"/>
+      <x:c r="L379" s="83"/>
     </x:row>
     <x:row r="380">
       <x:c r="G380" s="57"/>
@@ -3879,6 +4295,7 @@
       <x:c r="I380"/>
       <x:c r="J380"/>
       <x:c r="K380" s="64"/>
+      <x:c r="L380" s="83"/>
     </x:row>
     <x:row r="381">
       <x:c r="G381" s="57"/>
@@ -3886,6 +4303,7 @@
       <x:c r="I381"/>
       <x:c r="J381"/>
       <x:c r="K381" s="64"/>
+      <x:c r="L381" s="83"/>
     </x:row>
     <x:row r="382">
       <x:c r="G382" s="57"/>
@@ -3893,6 +4311,7 @@
       <x:c r="I382"/>
       <x:c r="J382"/>
       <x:c r="K382" s="64"/>
+      <x:c r="L382" s="83"/>
     </x:row>
     <x:row r="383">
       <x:c r="G383" s="57"/>
@@ -3900,6 +4319,7 @@
       <x:c r="I383"/>
       <x:c r="J383"/>
       <x:c r="K383" s="64"/>
+      <x:c r="L383" s="83"/>
     </x:row>
     <x:row r="384">
       <x:c r="G384" s="57"/>
@@ -3907,6 +4327,7 @@
       <x:c r="I384"/>
       <x:c r="J384"/>
       <x:c r="K384" s="64"/>
+      <x:c r="L384" s="83"/>
     </x:row>
     <x:row r="385">
       <x:c r="G385" s="57"/>
@@ -3914,6 +4335,7 @@
       <x:c r="I385"/>
       <x:c r="J385"/>
       <x:c r="K385" s="64"/>
+      <x:c r="L385" s="83"/>
     </x:row>
     <x:row r="386">
       <x:c r="G386" s="57"/>
@@ -3921,6 +4343,7 @@
       <x:c r="I386"/>
       <x:c r="J386"/>
       <x:c r="K386" s="64"/>
+      <x:c r="L386" s="83"/>
     </x:row>
     <x:row r="387">
       <x:c r="G387" s="57"/>
@@ -3928,6 +4351,7 @@
       <x:c r="I387"/>
       <x:c r="J387"/>
       <x:c r="K387" s="64"/>
+      <x:c r="L387" s="83"/>
     </x:row>
     <x:row r="388">
       <x:c r="G388" s="57"/>
@@ -3935,6 +4359,7 @@
       <x:c r="I388"/>
       <x:c r="J388"/>
       <x:c r="K388" s="64"/>
+      <x:c r="L388" s="83"/>
     </x:row>
     <x:row r="389">
       <x:c r="G389" s="57"/>
@@ -3942,6 +4367,7 @@
       <x:c r="I389"/>
       <x:c r="J389"/>
       <x:c r="K389" s="64"/>
+      <x:c r="L389" s="83"/>
     </x:row>
     <x:row r="390">
       <x:c r="G390" s="57"/>
@@ -3949,6 +4375,7 @@
       <x:c r="I390"/>
       <x:c r="J390"/>
       <x:c r="K390" s="64"/>
+      <x:c r="L390" s="83"/>
     </x:row>
     <x:row r="391">
       <x:c r="G391" s="57"/>
@@ -3956,6 +4383,7 @@
       <x:c r="I391"/>
       <x:c r="J391"/>
       <x:c r="K391" s="64"/>
+      <x:c r="L391" s="83"/>
     </x:row>
     <x:row r="392">
       <x:c r="G392" s="57"/>
@@ -3963,6 +4391,7 @@
       <x:c r="I392"/>
       <x:c r="J392"/>
       <x:c r="K392" s="64"/>
+      <x:c r="L392" s="83"/>
     </x:row>
     <x:row r="393">
       <x:c r="G393" s="57"/>
@@ -3970,6 +4399,7 @@
       <x:c r="I393"/>
       <x:c r="J393"/>
       <x:c r="K393" s="64"/>
+      <x:c r="L393" s="83"/>
     </x:row>
     <x:row r="394">
       <x:c r="G394" s="57"/>
@@ -3977,6 +4407,7 @@
       <x:c r="I394"/>
       <x:c r="J394"/>
       <x:c r="K394" s="64"/>
+      <x:c r="L394" s="83"/>
     </x:row>
     <x:row r="395">
       <x:c r="G395" s="57"/>
@@ -3984,6 +4415,7 @@
       <x:c r="I395"/>
       <x:c r="J395"/>
       <x:c r="K395" s="64"/>
+      <x:c r="L395" s="83"/>
     </x:row>
     <x:row r="396">
       <x:c r="G396" s="57"/>
@@ -3991,6 +4423,7 @@
       <x:c r="I396"/>
       <x:c r="J396"/>
       <x:c r="K396" s="64"/>
+      <x:c r="L396" s="83"/>
     </x:row>
     <x:row r="397">
       <x:c r="G397" s="57"/>
@@ -3998,6 +4431,7 @@
       <x:c r="I397"/>
       <x:c r="J397"/>
       <x:c r="K397" s="64"/>
+      <x:c r="L397" s="83"/>
     </x:row>
     <x:row r="398">
       <x:c r="G398" s="57"/>
@@ -4005,6 +4439,7 @@
       <x:c r="I398"/>
       <x:c r="J398"/>
       <x:c r="K398" s="64"/>
+      <x:c r="L398" s="83"/>
     </x:row>
     <x:row r="399">
       <x:c r="G399" s="57"/>
@@ -4012,6 +4447,7 @@
       <x:c r="I399"/>
       <x:c r="J399"/>
       <x:c r="K399" s="64"/>
+      <x:c r="L399" s="83"/>
     </x:row>
     <x:row r="400">
       <x:c r="G400" s="57"/>
@@ -4019,6 +4455,7 @@
       <x:c r="I400"/>
       <x:c r="J400"/>
       <x:c r="K400" s="64"/>
+      <x:c r="L400" s="83"/>
     </x:row>
     <x:row r="401">
       <x:c r="G401" s="57"/>
@@ -4026,6 +4463,7 @@
       <x:c r="I401"/>
       <x:c r="J401"/>
       <x:c r="K401" s="64"/>
+      <x:c r="L401" s="83"/>
     </x:row>
     <x:row r="402">
       <x:c r="G402" s="57"/>
@@ -4033,6 +4471,7 @@
       <x:c r="I402"/>
       <x:c r="J402"/>
       <x:c r="K402" s="64"/>
+      <x:c r="L402" s="83"/>
     </x:row>
     <x:row r="403">
       <x:c r="G403" s="57"/>
@@ -4040,6 +4479,7 @@
       <x:c r="I403"/>
       <x:c r="J403"/>
       <x:c r="K403" s="64"/>
+      <x:c r="L403" s="83"/>
     </x:row>
     <x:row r="404">
       <x:c r="G404" s="57"/>
@@ -4047,6 +4487,7 @@
       <x:c r="I404"/>
       <x:c r="J404"/>
       <x:c r="K404" s="64"/>
+      <x:c r="L404" s="83"/>
     </x:row>
     <x:row r="405">
       <x:c r="G405" s="57"/>
@@ -4054,6 +4495,7 @@
       <x:c r="I405"/>
       <x:c r="J405"/>
       <x:c r="K405" s="64"/>
+      <x:c r="L405" s="83"/>
     </x:row>
     <x:row r="406">
       <x:c r="G406" s="57"/>
@@ -4061,6 +4503,7 @@
       <x:c r="I406"/>
       <x:c r="J406"/>
       <x:c r="K406" s="64"/>
+      <x:c r="L406" s="83"/>
     </x:row>
     <x:row r="407">
       <x:c r="G407" s="57"/>
@@ -4068,6 +4511,7 @@
       <x:c r="I407"/>
       <x:c r="J407"/>
       <x:c r="K407" s="64"/>
+      <x:c r="L407" s="83"/>
     </x:row>
     <x:row r="408">
       <x:c r="G408" s="57"/>
@@ -4075,6 +4519,7 @@
       <x:c r="I408"/>
       <x:c r="J408"/>
       <x:c r="K408" s="64"/>
+      <x:c r="L408" s="83"/>
     </x:row>
     <x:row r="409">
       <x:c r="G409" s="57"/>
@@ -4082,6 +4527,7 @@
       <x:c r="I409"/>
       <x:c r="J409"/>
       <x:c r="K409" s="64"/>
+      <x:c r="L409" s="83"/>
     </x:row>
     <x:row r="410">
       <x:c r="G410" s="57"/>
@@ -4089,6 +4535,7 @@
       <x:c r="I410"/>
       <x:c r="J410"/>
       <x:c r="K410" s="64"/>
+      <x:c r="L410" s="83"/>
     </x:row>
     <x:row r="411">
       <x:c r="G411" s="57"/>
@@ -4096,6 +4543,7 @@
       <x:c r="I411"/>
       <x:c r="J411"/>
       <x:c r="K411" s="64"/>
+      <x:c r="L411" s="83"/>
     </x:row>
     <x:row r="412">
       <x:c r="G412" s="57"/>
@@ -4103,6 +4551,7 @@
       <x:c r="I412"/>
       <x:c r="J412"/>
       <x:c r="K412" s="64"/>
+      <x:c r="L412" s="83"/>
     </x:row>
     <x:row r="413">
       <x:c r="G413" s="57"/>
@@ -4110,6 +4559,7 @@
       <x:c r="I413"/>
       <x:c r="J413"/>
       <x:c r="K413" s="64"/>
+      <x:c r="L413" s="83"/>
     </x:row>
     <x:row r="414">
       <x:c r="G414" s="57"/>
@@ -4117,6 +4567,7 @@
       <x:c r="I414"/>
       <x:c r="J414"/>
       <x:c r="K414" s="64"/>
+      <x:c r="L414" s="83"/>
     </x:row>
     <x:row r="415">
       <x:c r="G415" s="57"/>
@@ -4124,6 +4575,7 @@
       <x:c r="I415"/>
       <x:c r="J415"/>
       <x:c r="K415" s="64"/>
+      <x:c r="L415" s="83"/>
     </x:row>
     <x:row r="416">
       <x:c r="G416" s="57"/>
@@ -4131,6 +4583,7 @@
       <x:c r="I416"/>
       <x:c r="J416"/>
       <x:c r="K416" s="64"/>
+      <x:c r="L416" s="83"/>
     </x:row>
     <x:row r="417">
       <x:c r="G417" s="57"/>
@@ -4138,6 +4591,7 @@
       <x:c r="I417"/>
       <x:c r="J417"/>
       <x:c r="K417" s="64"/>
+      <x:c r="L417" s="83"/>
     </x:row>
     <x:row r="418">
       <x:c r="G418" s="57"/>
@@ -4145,6 +4599,7 @@
       <x:c r="I418"/>
       <x:c r="J418"/>
       <x:c r="K418" s="64"/>
+      <x:c r="L418" s="83"/>
     </x:row>
     <x:row r="419">
       <x:c r="G419" s="57"/>
@@ -4152,6 +4607,7 @@
       <x:c r="I419"/>
       <x:c r="J419"/>
       <x:c r="K419" s="64"/>
+      <x:c r="L419" s="83"/>
     </x:row>
     <x:row r="420">
       <x:c r="G420" s="57"/>
@@ -4159,6 +4615,7 @@
       <x:c r="I420"/>
       <x:c r="J420"/>
       <x:c r="K420" s="64"/>
+      <x:c r="L420" s="83"/>
     </x:row>
     <x:row r="421">
       <x:c r="G421" s="57"/>
@@ -4166,6 +4623,7 @@
       <x:c r="I421"/>
       <x:c r="J421"/>
       <x:c r="K421" s="64"/>
+      <x:c r="L421" s="83"/>
     </x:row>
     <x:row r="422">
       <x:c r="G422" s="57"/>
@@ -4173,6 +4631,7 @@
       <x:c r="I422"/>
       <x:c r="J422"/>
       <x:c r="K422" s="64"/>
+      <x:c r="L422" s="83"/>
     </x:row>
     <x:row r="423">
       <x:c r="G423" s="57"/>
@@ -4180,6 +4639,7 @@
       <x:c r="I423"/>
       <x:c r="J423"/>
       <x:c r="K423" s="64"/>
+      <x:c r="L423" s="83"/>
     </x:row>
     <x:row r="424">
       <x:c r="G424" s="57"/>
@@ -4187,6 +4647,7 @@
       <x:c r="I424"/>
       <x:c r="J424"/>
       <x:c r="K424" s="64"/>
+      <x:c r="L424" s="83"/>
     </x:row>
     <x:row r="425">
       <x:c r="G425" s="57"/>
@@ -4194,6 +4655,7 @@
       <x:c r="I425"/>
       <x:c r="J425"/>
       <x:c r="K425" s="64"/>
+      <x:c r="L425" s="83"/>
     </x:row>
     <x:row r="426">
       <x:c r="G426" s="57"/>
@@ -4201,6 +4663,7 @@
       <x:c r="I426"/>
       <x:c r="J426"/>
       <x:c r="K426" s="64"/>
+      <x:c r="L426" s="83"/>
     </x:row>
     <x:row r="427">
       <x:c r="G427" s="57"/>
@@ -4208,6 +4671,7 @@
       <x:c r="I427"/>
       <x:c r="J427"/>
       <x:c r="K427" s="64"/>
+      <x:c r="L427" s="83"/>
     </x:row>
     <x:row r="428">
       <x:c r="G428" s="57"/>
@@ -4215,6 +4679,7 @@
       <x:c r="I428"/>
       <x:c r="J428"/>
       <x:c r="K428" s="64"/>
+      <x:c r="L428" s="83"/>
     </x:row>
     <x:row r="429">
       <x:c r="G429" s="57"/>
@@ -4222,6 +4687,7 @@
       <x:c r="I429"/>
       <x:c r="J429"/>
       <x:c r="K429" s="64"/>
+      <x:c r="L429" s="83"/>
     </x:row>
     <x:row r="430">
       <x:c r="G430" s="57"/>
@@ -4229,6 +4695,7 @@
       <x:c r="I430"/>
       <x:c r="J430"/>
       <x:c r="K430" s="64"/>
+      <x:c r="L430" s="83"/>
     </x:row>
     <x:row r="431">
       <x:c r="G431" s="57"/>
@@ -4236,6 +4703,7 @@
       <x:c r="I431"/>
       <x:c r="J431"/>
       <x:c r="K431" s="64"/>
+      <x:c r="L431" s="83"/>
     </x:row>
     <x:row r="432">
       <x:c r="G432" s="57"/>
@@ -4243,6 +4711,7 @@
       <x:c r="I432"/>
       <x:c r="J432"/>
       <x:c r="K432" s="64"/>
+      <x:c r="L432" s="83"/>
     </x:row>
     <x:row r="433">
       <x:c r="G433" s="57"/>
@@ -4250,6 +4719,7 @@
       <x:c r="I433"/>
       <x:c r="J433"/>
       <x:c r="K433" s="64"/>
+      <x:c r="L433" s="83"/>
     </x:row>
     <x:row r="434">
       <x:c r="G434" s="57"/>
@@ -4257,6 +4727,7 @@
       <x:c r="I434"/>
       <x:c r="J434"/>
       <x:c r="K434" s="64"/>
+      <x:c r="L434" s="83"/>
     </x:row>
     <x:row r="435">
       <x:c r="G435" s="57"/>
@@ -4264,6 +4735,7 @@
       <x:c r="I435"/>
       <x:c r="J435"/>
       <x:c r="K435" s="64"/>
+      <x:c r="L435" s="83"/>
     </x:row>
     <x:row r="436">
       <x:c r="G436" s="57"/>
@@ -4271,6 +4743,7 @@
       <x:c r="I436"/>
       <x:c r="J436"/>
       <x:c r="K436" s="64"/>
+      <x:c r="L436" s="83"/>
     </x:row>
     <x:row r="437">
       <x:c r="G437" s="57"/>
@@ -4278,6 +4751,7 @@
       <x:c r="I437"/>
       <x:c r="J437"/>
       <x:c r="K437" s="64"/>
+      <x:c r="L437" s="83"/>
     </x:row>
     <x:row r="438">
       <x:c r="G438" s="57"/>
@@ -4285,6 +4759,7 @@
       <x:c r="I438"/>
       <x:c r="J438"/>
       <x:c r="K438" s="64"/>
+      <x:c r="L438" s="83"/>
     </x:row>
     <x:row r="439">
       <x:c r="G439" s="57"/>
@@ -4292,6 +4767,7 @@
       <x:c r="I439"/>
       <x:c r="J439"/>
       <x:c r="K439" s="64"/>
+      <x:c r="L439" s="83"/>
     </x:row>
     <x:row r="440">
       <x:c r="G440" s="57"/>
@@ -4299,6 +4775,7 @@
       <x:c r="I440"/>
       <x:c r="J440"/>
       <x:c r="K440" s="64"/>
+      <x:c r="L440" s="83"/>
     </x:row>
     <x:row r="441">
       <x:c r="G441" s="57"/>
@@ -4306,6 +4783,7 @@
       <x:c r="I441"/>
       <x:c r="J441"/>
       <x:c r="K441" s="64"/>
+      <x:c r="L441" s="83"/>
     </x:row>
     <x:row r="442">
       <x:c r="G442" s="57"/>
@@ -4313,6 +4791,7 @@
       <x:c r="I442"/>
       <x:c r="J442"/>
       <x:c r="K442" s="64"/>
+      <x:c r="L442" s="83"/>
     </x:row>
     <x:row r="443">
       <x:c r="G443" s="57"/>
@@ -4320,6 +4799,7 @@
       <x:c r="I443"/>
       <x:c r="J443"/>
       <x:c r="K443" s="64"/>
+      <x:c r="L443" s="83"/>
     </x:row>
     <x:row r="444">
       <x:c r="G444" s="57"/>
@@ -4327,6 +4807,7 @@
       <x:c r="I444"/>
       <x:c r="J444"/>
       <x:c r="K444" s="64"/>
+      <x:c r="L444" s="83"/>
     </x:row>
     <x:row r="445">
       <x:c r="G445" s="57"/>
@@ -4334,6 +4815,7 @@
       <x:c r="I445"/>
       <x:c r="J445"/>
       <x:c r="K445" s="64"/>
+      <x:c r="L445" s="83"/>
     </x:row>
     <x:row r="446">
       <x:c r="G446" s="57"/>
@@ -4341,6 +4823,7 @@
       <x:c r="I446"/>
       <x:c r="J446"/>
       <x:c r="K446" s="64"/>
+      <x:c r="L446" s="83"/>
     </x:row>
     <x:row r="447">
       <x:c r="G447" s="57"/>
@@ -4348,6 +4831,7 @@
       <x:c r="I447"/>
       <x:c r="J447"/>
       <x:c r="K447" s="64"/>
+      <x:c r="L447" s="83"/>
     </x:row>
     <x:row r="448">
       <x:c r="G448" s="57"/>
@@ -4355,6 +4839,7 @@
       <x:c r="I448"/>
       <x:c r="J448"/>
       <x:c r="K448" s="64"/>
+      <x:c r="L448" s="83"/>
     </x:row>
     <x:row r="449">
       <x:c r="G449" s="57"/>
@@ -4362,6 +4847,7 @@
       <x:c r="I449"/>
       <x:c r="J449"/>
       <x:c r="K449" s="64"/>
+      <x:c r="L449" s="83"/>
     </x:row>
     <x:row r="450">
       <x:c r="G450" s="57"/>
@@ -4369,6 +4855,7 @@
       <x:c r="I450"/>
       <x:c r="J450"/>
       <x:c r="K450" s="64"/>
+      <x:c r="L450" s="83"/>
     </x:row>
     <x:row r="451">
       <x:c r="G451" s="57"/>
@@ -4376,6 +4863,7 @@
       <x:c r="I451"/>
       <x:c r="J451"/>
       <x:c r="K451" s="64"/>
+      <x:c r="L451" s="83"/>
     </x:row>
     <x:row r="452">
       <x:c r="G452" s="57"/>
@@ -4383,6 +4871,7 @@
       <x:c r="I452"/>
       <x:c r="J452"/>
       <x:c r="K452" s="64"/>
+      <x:c r="L452" s="83"/>
     </x:row>
     <x:row r="453">
       <x:c r="G453" s="57"/>
@@ -4390,6 +4879,7 @@
       <x:c r="I453"/>
       <x:c r="J453"/>
       <x:c r="K453" s="64"/>
+      <x:c r="L453" s="83"/>
     </x:row>
     <x:row r="454">
       <x:c r="G454" s="57"/>
@@ -4397,6 +4887,7 @@
       <x:c r="I454"/>
       <x:c r="J454"/>
       <x:c r="K454" s="64"/>
+      <x:c r="L454" s="83"/>
     </x:row>
     <x:row r="455">
       <x:c r="G455" s="57"/>
@@ -4404,6 +4895,7 @@
       <x:c r="I455"/>
       <x:c r="J455"/>
       <x:c r="K455" s="64"/>
+      <x:c r="L455" s="83"/>
     </x:row>
     <x:row r="456">
       <x:c r="G456" s="57"/>
@@ -4411,6 +4903,7 @@
       <x:c r="I456"/>
       <x:c r="J456"/>
       <x:c r="K456" s="64"/>
+      <x:c r="L456" s="83"/>
     </x:row>
     <x:row r="457">
       <x:c r="G457" s="57"/>
@@ -4418,6 +4911,7 @@
       <x:c r="I457"/>
       <x:c r="J457"/>
       <x:c r="K457" s="64"/>
+      <x:c r="L457" s="83"/>
     </x:row>
     <x:row r="458">
       <x:c r="G458" s="57"/>
@@ -4425,6 +4919,7 @@
       <x:c r="I458"/>
       <x:c r="J458"/>
       <x:c r="K458" s="64"/>
+      <x:c r="L458" s="83"/>
     </x:row>
     <x:row r="459">
       <x:c r="G459" s="57"/>
@@ -4432,6 +4927,7 @@
       <x:c r="I459"/>
       <x:c r="J459"/>
       <x:c r="K459" s="64"/>
+      <x:c r="L459" s="83"/>
     </x:row>
     <x:row r="460">
       <x:c r="G460" s="57"/>
@@ -4439,6 +4935,7 @@
       <x:c r="I460"/>
       <x:c r="J460"/>
       <x:c r="K460" s="64"/>
+      <x:c r="L460" s="83"/>
     </x:row>
     <x:row r="461">
       <x:c r="G461" s="57"/>
@@ -4446,6 +4943,7 @@
       <x:c r="I461"/>
       <x:c r="J461"/>
       <x:c r="K461" s="64"/>
+      <x:c r="L461" s="83"/>
     </x:row>
     <x:row r="462">
       <x:c r="G462" s="57"/>
@@ -4453,6 +4951,7 @@
       <x:c r="I462"/>
       <x:c r="J462"/>
       <x:c r="K462" s="64"/>
+      <x:c r="L462" s="83"/>
     </x:row>
     <x:row r="463">
       <x:c r="G463" s="57"/>
@@ -4460,6 +4959,7 @@
       <x:c r="I463"/>
       <x:c r="J463"/>
       <x:c r="K463" s="64"/>
+      <x:c r="L463" s="83"/>
     </x:row>
     <x:row r="464">
       <x:c r="G464" s="57"/>
@@ -4467,6 +4967,7 @@
       <x:c r="I464"/>
       <x:c r="J464"/>
       <x:c r="K464" s="64"/>
+      <x:c r="L464" s="83"/>
     </x:row>
     <x:row r="465">
       <x:c r="G465" s="57"/>
@@ -4474,6 +4975,7 @@
       <x:c r="I465"/>
       <x:c r="J465"/>
       <x:c r="K465" s="64"/>
+      <x:c r="L465" s="83"/>
     </x:row>
     <x:row r="466">
       <x:c r="G466" s="57"/>
@@ -4481,6 +4983,7 @@
       <x:c r="I466"/>
       <x:c r="J466"/>
       <x:c r="K466" s="64"/>
+      <x:c r="L466" s="83"/>
     </x:row>
     <x:row r="467">
       <x:c r="G467" s="57"/>
@@ -4488,6 +4991,7 @@
       <x:c r="I467"/>
       <x:c r="J467"/>
       <x:c r="K467" s="64"/>
+      <x:c r="L467" s="83"/>
     </x:row>
     <x:row r="468">
       <x:c r="G468" s="57"/>
@@ -4495,6 +4999,7 @@
       <x:c r="I468"/>
       <x:c r="J468"/>
       <x:c r="K468" s="64"/>
+      <x:c r="L468" s="83"/>
     </x:row>
     <x:row r="469">
       <x:c r="G469" s="57"/>
@@ -4502,6 +5007,7 @@
       <x:c r="I469"/>
       <x:c r="J469"/>
       <x:c r="K469" s="64"/>
+      <x:c r="L469" s="83"/>
     </x:row>
     <x:row r="470">
       <x:c r="G470" s="57"/>
@@ -4509,6 +5015,7 @@
       <x:c r="I470"/>
       <x:c r="J470"/>
       <x:c r="K470" s="64"/>
+      <x:c r="L470" s="83"/>
     </x:row>
     <x:row r="471">
       <x:c r="G471" s="57"/>
@@ -4516,6 +5023,7 @@
       <x:c r="I471"/>
       <x:c r="J471"/>
       <x:c r="K471" s="64"/>
+      <x:c r="L471" s="83"/>
     </x:row>
     <x:row r="472">
       <x:c r="G472" s="57"/>
@@ -4523,6 +5031,7 @@
       <x:c r="I472"/>
       <x:c r="J472"/>
       <x:c r="K472" s="64"/>
+      <x:c r="L472" s="83"/>
     </x:row>
     <x:row r="473">
       <x:c r="G473" s="57"/>
@@ -4530,6 +5039,7 @@
       <x:c r="I473"/>
       <x:c r="J473"/>
       <x:c r="K473" s="64"/>
+      <x:c r="L473" s="83"/>
     </x:row>
     <x:row r="474">
       <x:c r="G474" s="57"/>
@@ -4537,6 +5047,7 @@
       <x:c r="I474"/>
       <x:c r="J474"/>
       <x:c r="K474" s="64"/>
+      <x:c r="L474" s="83"/>
     </x:row>
     <x:row r="475">
       <x:c r="G475" s="57"/>
@@ -4544,6 +5055,7 @@
       <x:c r="I475"/>
       <x:c r="J475"/>
       <x:c r="K475" s="64"/>
+      <x:c r="L475" s="83"/>
     </x:row>
     <x:row r="476">
       <x:c r="G476" s="57"/>
@@ -4551,6 +5063,7 @@
       <x:c r="I476"/>
       <x:c r="J476"/>
       <x:c r="K476" s="64"/>
+      <x:c r="L476" s="83"/>
     </x:row>
     <x:row r="477">
       <x:c r="G477" s="57"/>
@@ -4558,6 +5071,7 @@
       <x:c r="I477"/>
       <x:c r="J477"/>
       <x:c r="K477" s="64"/>
+      <x:c r="L477" s="83"/>
     </x:row>
     <x:row r="478">
       <x:c r="G478" s="57"/>
@@ -4565,6 +5079,7 @@
       <x:c r="I478"/>
       <x:c r="J478"/>
       <x:c r="K478" s="64"/>
+      <x:c r="L478" s="83"/>
     </x:row>
     <x:row r="479">
       <x:c r="G479" s="57"/>
@@ -4572,6 +5087,7 @@
       <x:c r="I479"/>
       <x:c r="J479"/>
       <x:c r="K479" s="64"/>
+      <x:c r="L479" s="83"/>
     </x:row>
     <x:row r="480">
       <x:c r="G480" s="57"/>
@@ -4579,6 +5095,7 @@
       <x:c r="I480"/>
       <x:c r="J480"/>
       <x:c r="K480" s="64"/>
+      <x:c r="L480" s="83"/>
     </x:row>
     <x:row r="481">
       <x:c r="G481" s="57"/>
@@ -4586,6 +5103,7 @@
       <x:c r="I481"/>
       <x:c r="J481"/>
       <x:c r="K481" s="64"/>
+      <x:c r="L481" s="83"/>
     </x:row>
     <x:row r="482">
       <x:c r="G482" s="57"/>
@@ -4593,6 +5111,7 @@
       <x:c r="I482"/>
       <x:c r="J482"/>
       <x:c r="K482" s="64"/>
+      <x:c r="L482" s="83"/>
     </x:row>
     <x:row r="483">
       <x:c r="G483" s="57"/>
@@ -4600,6 +5119,7 @@
       <x:c r="I483"/>
       <x:c r="J483"/>
       <x:c r="K483" s="64"/>
+      <x:c r="L483" s="83"/>
     </x:row>
     <x:row r="484">
       <x:c r="G484" s="57"/>
@@ -4607,6 +5127,7 @@
       <x:c r="I484"/>
       <x:c r="J484"/>
       <x:c r="K484" s="64"/>
+      <x:c r="L484" s="83"/>
     </x:row>
     <x:row r="485">
       <x:c r="G485" s="57"/>
@@ -4614,6 +5135,7 @@
       <x:c r="I485"/>
       <x:c r="J485"/>
       <x:c r="K485" s="64"/>
+      <x:c r="L485" s="83"/>
     </x:row>
     <x:row r="486">
       <x:c r="G486" s="57"/>
@@ -4621,6 +5143,7 @@
       <x:c r="I486"/>
       <x:c r="J486"/>
       <x:c r="K486" s="64"/>
+      <x:c r="L486" s="83"/>
     </x:row>
     <x:row r="487">
       <x:c r="G487" s="57"/>
@@ -4628,6 +5151,7 @@
       <x:c r="I487"/>
       <x:c r="J487"/>
       <x:c r="K487" s="64"/>
+      <x:c r="L487" s="83"/>
     </x:row>
     <x:row r="488">
       <x:c r="G488" s="57"/>
@@ -4635,6 +5159,7 @@
       <x:c r="I488"/>
       <x:c r="J488"/>
       <x:c r="K488" s="64"/>
+      <x:c r="L488" s="83"/>
     </x:row>
     <x:row r="489">
       <x:c r="G489" s="57"/>
@@ -4642,6 +5167,7 @@
       <x:c r="I489"/>
       <x:c r="J489"/>
       <x:c r="K489" s="64"/>
+      <x:c r="L489" s="83"/>
     </x:row>
     <x:row r="490">
       <x:c r="G490" s="57"/>
@@ -4649,6 +5175,7 @@
       <x:c r="I490"/>
       <x:c r="J490"/>
       <x:c r="K490" s="64"/>
+      <x:c r="L490" s="83"/>
     </x:row>
     <x:row r="491">
       <x:c r="G491" s="57"/>
@@ -4656,6 +5183,7 @@
       <x:c r="I491"/>
       <x:c r="J491"/>
       <x:c r="K491" s="64"/>
+      <x:c r="L491" s="83"/>
     </x:row>
     <x:row r="492">
       <x:c r="G492" s="57"/>
@@ -4663,6 +5191,7 @@
       <x:c r="I492"/>
       <x:c r="J492"/>
       <x:c r="K492" s="64"/>
+      <x:c r="L492" s="83"/>
     </x:row>
     <x:row r="493">
       <x:c r="G493" s="57"/>
@@ -4670,6 +5199,7 @@
       <x:c r="I493"/>
       <x:c r="J493"/>
       <x:c r="K493" s="64"/>
+      <x:c r="L493" s="83"/>
     </x:row>
     <x:row r="494">
       <x:c r="G494" s="57"/>
@@ -4677,6 +5207,7 @@
       <x:c r="I494"/>
       <x:c r="J494"/>
       <x:c r="K494" s="64"/>
+      <x:c r="L494" s="83"/>
     </x:row>
     <x:row r="495">
       <x:c r="G495" s="57"/>
@@ -4684,6 +5215,7 @@
       <x:c r="I495"/>
       <x:c r="J495"/>
       <x:c r="K495" s="64"/>
+      <x:c r="L495" s="83"/>
     </x:row>
     <x:row r="496">
       <x:c r="G496" s="57"/>
@@ -4691,6 +5223,7 @@
       <x:c r="I496"/>
       <x:c r="J496"/>
       <x:c r="K496" s="64"/>
+      <x:c r="L496" s="83"/>
     </x:row>
     <x:row r="497">
       <x:c r="G497" s="57"/>
@@ -4698,6 +5231,7 @@
       <x:c r="I497"/>
       <x:c r="J497"/>
       <x:c r="K497" s="64"/>
+      <x:c r="L497" s="83"/>
     </x:row>
     <x:row r="498">
       <x:c r="G498" s="57"/>
@@ -4705,6 +5239,7 @@
       <x:c r="I498"/>
       <x:c r="J498"/>
       <x:c r="K498" s="64"/>
+      <x:c r="L498" s="83"/>
     </x:row>
     <x:row r="499">
       <x:c r="G499" s="57"/>
@@ -4712,6 +5247,7 @@
       <x:c r="I499"/>
       <x:c r="J499"/>
       <x:c r="K499" s="64"/>
+      <x:c r="L499" s="83"/>
     </x:row>
     <x:row r="500">
       <x:c r="G500" s="57"/>
@@ -4719,6 +5255,7 @@
       <x:c r="I500"/>
       <x:c r="J500"/>
       <x:c r="K500" s="64"/>
+      <x:c r="L500" s="83"/>
     </x:row>
     <x:row r="501">
       <x:c r="G501" s="57"/>
@@ -4726,14 +5263,18 @@
       <x:c r="I501"/>
       <x:c r="J501"/>
       <x:c r="K501" s="65"/>
+      <x:c r="L501" s="84"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="B2:B101">
       <x:formula1>"student,faculty,school personnel"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="G2:G501">
       <x:formula1>"Male,Female,Other"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="L2:L501">
+      <x:formula1>"Applicant,Official"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4843,8 +5384,12 @@
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="51"/>
-      <x:c r="B13" s="52"/>
+      <x:c r="A13" s="51" t="str">
+        <x:v>Access Status</x:v>
+      </x:c>
+      <x:c r="B13" s="52" t="str">
+        <x:v>Required. Use Applicant for APE and records access only, or Official to enable Health Passport and appointment booking immediately. Applicants become Official after final APE clearance.</x:v>
+      </x:c>
       <x:c r="C13" s="52"/>
       <x:c r="D13" s="52"/>
       <x:c r="E13" s="52"/>
